--- a/AAII_Financials/Quarterly/AFRM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFRM_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
   <si>
     <t>AFRM</t>
   </si>
@@ -656,165 +656,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>538400</v>
+      </c>
+      <c r="E8" s="3">
         <v>462300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>413500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>348200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>340000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>298000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>308900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>302300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>303300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>238400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>219200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>214300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>189500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>157500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>141800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>128400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>125200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>82200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>69600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>73100</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -875,8 +881,11 @@
       <c r="V9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -937,8 +946,11 @@
       <c r="V10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,8 +973,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1023,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,70 +1101,76 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E14" s="3">
         <v>2200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>33300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-21200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-28000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-15000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-5600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>20700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>24300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>57200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>55200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>49400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>43700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>33700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>37900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>14200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>22000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1209,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>710600</v>
+      </c>
+      <c r="E17" s="3">
         <v>671700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>657300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>658200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>699500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>585500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>586100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>528800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>499500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>404500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>333500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>423700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>216300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>190800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>102400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>209900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>157900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>115200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>110300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-172200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-209400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-243800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-310000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-359500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-287500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-277200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-226500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-196200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-166100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-114300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-209400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-26800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-33300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>39400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-81500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-32700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-33000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-40700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-20300</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,132 +1410,139 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E20" s="3">
         <v>38700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>36500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>103500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>35500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>36000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>72700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>172100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>36800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-140400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-11600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-77800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>29500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>4300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-141100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-130600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-164000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-159000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-301000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-230600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-187400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-41300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-147500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-295900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-118000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-282100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-23200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-100</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" s="3">
         <v>-28600</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1564,108 +1603,114 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-167600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-170700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-207300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-206500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-324000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-251400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-204500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-54400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-159500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-306400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-125900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-287100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-26500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>34900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-85500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-30900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-30700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-36400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-19700</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E24" s="3">
         <v>1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-18100</v>
-      </c>
-      <c r="J24" s="3">
-        <v>300</v>
       </c>
       <c r="K24" s="3">
         <v>300</v>
       </c>
       <c r="L24" s="3">
+        <v>300</v>
+      </c>
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
-      </c>
-      <c r="O24" s="3">
-        <v>100</v>
       </c>
       <c r="P24" s="3">
         <v>100</v>
@@ -1683,13 +1728,16 @@
         <v>100</v>
       </c>
       <c r="U24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-166900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-171800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-206000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-205700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-322400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-251300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-186400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-54700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-159700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-306600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-123400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-287100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-26600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>34800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-85600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-31000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-30800</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-166900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-171800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-206000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-205700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-322400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-251300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-186400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-54700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-159700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-306600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-123400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-287100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-26600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>34800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-85600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-44200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-30800</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,132 +2188,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-38700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-36500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-103500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-35500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-36000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-72700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-172100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-36800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>140400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>11600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>77800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-29500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-4300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-166900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-171800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-206000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-205700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-322400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-251300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-186400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-54700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-159700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-306600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-123400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-287100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-26600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>34800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-85600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-44200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-30800</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-166900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-171800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-206000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-205700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-322400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-251300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-186400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-54700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-159700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-306600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-123400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-287100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-26600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>34800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-85600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-44200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-30800</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,53 +2570,54 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1036700</v>
+      </c>
+      <c r="E41" s="3">
         <v>1079300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>892000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>972500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1440300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1530100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1255200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2261900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2567400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1439500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1466600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1623700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>520700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>684400</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>5</v>
       </c>
@@ -2547,8 +2633,11 @@
       <c r="V41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2609,53 +2698,56 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>307300</v>
+      </c>
+      <c r="E43" s="3">
         <v>236200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>199100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>135800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>201600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>147800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>142100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>124600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>134600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>101000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>91600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>66100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>67000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>49000</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>5</v>
       </c>
@@ -2671,8 +2763,11 @@
       <c r="V43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2733,47 +2828,50 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>70200</v>
+      </c>
+      <c r="E45" s="3">
         <v>29500</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3">
         <v>14300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>15100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>35200</v>
       </c>
       <c r="J45" s="3">
         <v>35200</v>
       </c>
       <c r="K45" s="3">
+        <v>35200</v>
+      </c>
+      <c r="L45" s="3">
         <v>37300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>23300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>111300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>90900</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>5</v>
       </c>
@@ -2789,14 +2887,17 @@
       <c r="T45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U45" s="3">
-        <v>0</v>
+      <c r="U45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2857,53 +2958,56 @@
       <c r="V46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>5928500</v>
+      </c>
+      <c r="E47" s="3">
         <v>5390900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5416300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4701400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4453200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3826600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4003900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3008600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2790300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2585000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1958400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2099100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1757700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1290300</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>5</v>
       </c>
@@ -2919,53 +3023,56 @@
       <c r="V47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>394900</v>
+      </c>
+      <c r="E48" s="3">
         <v>366000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>320300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>311200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>292600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>256200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>222200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>194000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>169400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>143500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>120300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>113100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>49400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>49600</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>5</v>
       </c>
@@ -2981,47 +3088,50 @@
       <c r="V48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>558600</v>
+      </c>
+      <c r="E49" s="3">
         <v>556200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>577000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>585400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>591400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>596000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>618500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>608300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>607600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>612100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>584400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>279200</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3037,14 +3147,17 @@
       <c r="T49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,53 +3283,56 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>444300</v>
+      </c>
+      <c r="E52" s="3">
         <v>434900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>403600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>439000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>459100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>422300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>335800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>440500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>298700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>256000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>260200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>216800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>137500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>112200</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3229,8 +3348,11 @@
       <c r="V52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,53 +3413,56 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9065000</v>
+      </c>
+      <c r="E54" s="3">
         <v>8407100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8155600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7507800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7804800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7165100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6973800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7031700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6952400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5402100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4867000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4766400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2708100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2250500</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>5</v>
       </c>
@@ -3353,8 +3478,11 @@
       <c r="V54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,53 +3530,54 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E57" s="3">
         <v>27300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>28600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>30000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>29000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>34500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>33100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>49000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>45600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>425900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>57800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>29000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>26200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>24500</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3463,8 +3593,11 @@
       <c r="V57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3525,53 +3658,56 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>255700</v>
+      </c>
+      <c r="E59" s="3">
         <v>220300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>170600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>154000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>249700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>220900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>211100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>151400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>213200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>180000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>200800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>177700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>80800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>49200</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>5</v>
       </c>
@@ -3587,8 +3723,11 @@
       <c r="V59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3649,53 +3788,56 @@
       <c r="V60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6063300</v>
+      </c>
+      <c r="E61" s="3">
         <v>5523600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5344600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4716300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4905700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4221200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4006800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4054400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3927900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2106500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1857300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2001500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1623400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1197800</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3711,8 +3853,11 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3773,8 +3918,11 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,53 +4113,56 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6430100</v>
+      </c>
+      <c r="E66" s="3">
         <v>5840300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5621400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4996700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5294600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4601600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4355500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4455700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4484100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3024700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2285800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2362400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1730400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1271500</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>5</v>
       </c>
@@ -4021,8 +4178,11 @@
       <c r="V66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4208,14 +4375,14 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>1327300</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>1327200</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -4231,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,53 +4463,56 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2929900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2763000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2591200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2385300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2179600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1857200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1605900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1419500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1364800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1205100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-888400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-734900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-494000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-462400</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>5</v>
       </c>
@@ -4355,8 +4528,11 @@
       <c r="V72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,53 +4723,56 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2634900</v>
+      </c>
+      <c r="E76" s="3">
         <v>2566800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2534200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2511100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2510100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2563400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2618300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2576100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2468300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2377400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2581200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2404000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-349600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-348100</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>5</v>
       </c>
@@ -4603,8 +4788,11 @@
       <c r="V76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-166900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-171800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-206000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-205700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-322400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-251300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-186400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-54700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-159700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-306600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-123400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-287100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-26600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>34800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-85600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-44200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-30800</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,53 +5015,54 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E83" s="3">
         <v>40100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>43300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>47500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>23000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>20900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>17100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>12000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>10500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3700</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>5</v>
       </c>
@@ -4880,8 +5078,11 @@
       <c r="V83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,53 +5403,56 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>74300</v>
+      </c>
+      <c r="E89" s="3">
         <v>98900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>43800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-54300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-28500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>51200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-59100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-28000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-440300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>365200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-19900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-123300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-47700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>5</v>
       </c>
@@ -5252,8 +5468,11 @@
       <c r="V89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,53 +5495,54 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-38700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-35800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-24900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-30500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-34300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-31200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-52500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-21100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-21800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-16300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>5</v>
       </c>
@@ -5338,8 +5558,11 @@
       <c r="V91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,53 +5688,56 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-624900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-15900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-777200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-301000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-692200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>117300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1025700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-166000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-190100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-629500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>84300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-199700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-548900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-357800</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>5</v>
       </c>
@@ -5524,8 +5753,11 @@
       <c r="V94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5610,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,53 +6038,56 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>506300</v>
+      </c>
+      <c r="E100" s="3">
         <v>148800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>609500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-129000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>669800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>199500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-28900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>55800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1766300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>244000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-176100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1488600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>447500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>817800</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>5</v>
       </c>
@@ -5858,44 +6103,47 @@
       <c r="V100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-3300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-11100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2700</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
@@ -5908,8 +6156,8 @@
       <c r="R101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -5920,53 +6168,56 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-40500</v>
+      </c>
+      <c r="E102" s="3">
         <v>228500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-121500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-483300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-48700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>362700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1124800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-139200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1139000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-16800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-114400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1170200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-149100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>457700</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>5</v>
       </c>
@@ -5980,6 +6231,9 @@
         <v>5</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AFRM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFRM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
   <si>
     <t>AFRM</t>
   </si>
@@ -656,171 +656,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>536000</v>
+      </c>
+      <c r="E8" s="3">
         <v>538400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>462300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>413500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>348200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>340000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>298000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>308900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>302300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>303300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>238400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>219200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>214300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>189500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>157500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>141800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>128400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>125200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>82200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>69600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>73100</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -884,8 +891,11 @@
       <c r="W9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -949,8 +959,11 @@
       <c r="W10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -974,8 +987,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1039,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,73 +1121,79 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E14" s="3">
         <v>1000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>33300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-21200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-28000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-15000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-5600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>7600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>20700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>24300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>57200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>55200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>49400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>43700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>33700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>37900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>14200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>22000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1234,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>696800</v>
+      </c>
+      <c r="E17" s="3">
         <v>710600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>671700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>657300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>658200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>699500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>585500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>586100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>528800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>499500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>404500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>333500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>423700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>216300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>190800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>102400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>209900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>157900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>115200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>110300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-160800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-172200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-209400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-243800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-310000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-359500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-287500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-277200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-226500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-196200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-166100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-114300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-209400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-26800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-33300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>39400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-81500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-32700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-33000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-40700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-20300</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,138 +1444,145 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E20" s="3">
         <v>4600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>38700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>36500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>103500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>35500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>36000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>72700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>172100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>36800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-140400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-11600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-77800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>29500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>4300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-96000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-141100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-130600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-164000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-159000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-301000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-230600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-187400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-41300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-147500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-295900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-118000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-282100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-23200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-100</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3">
         <v>-28600</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1606,114 +1646,120 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-133000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-167600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-170700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-207300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-206500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-324000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-251400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-204500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-54400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-159500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-306400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-125900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-287100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-26500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>34900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-85500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-30900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-30700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-36400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-19700</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-18100</v>
-      </c>
-      <c r="K24" s="3">
-        <v>300</v>
       </c>
       <c r="L24" s="3">
         <v>300</v>
       </c>
       <c r="M24" s="3">
+        <v>300</v>
+      </c>
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
-      </c>
-      <c r="P24" s="3">
-        <v>100</v>
       </c>
       <c r="Q24" s="3">
         <v>100</v>
@@ -1731,13 +1777,16 @@
         <v>100</v>
       </c>
       <c r="V24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-133900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-166900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-171800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-206000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-205700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-322400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-251300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-186400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-54700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-159700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-306600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-123400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-287100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>34800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-85600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-31000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-30800</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-133900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-166900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-171800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-206000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-205700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-322400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-251300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-186400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-54700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-159700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-306600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-123400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-287100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>34800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-85600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-44200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-30800</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,138 +2258,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-27700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-38700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-36500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-103500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-35500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-36000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-72700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-172100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-36800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>140400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>11600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>77800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-29500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-4300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-133900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-166900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-171800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-206000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-205700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-322400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-251300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-186400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-54700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-159700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-306600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-123400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-287100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>34800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-85600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-44200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-30800</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-133900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-166900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-171800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-206000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-205700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-322400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-251300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-186400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-54700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-159700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-306600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-123400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-287100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>34800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-85600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-44200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-30800</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,56 +2657,57 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1272800</v>
+      </c>
+      <c r="E41" s="3">
         <v>1036700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1079300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>892000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>972500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1440300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1530100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1255200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2261900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2567400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1439500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1466600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1623700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>520700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>684400</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>5</v>
       </c>
@@ -2636,8 +2723,11 @@
       <c r="W41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2701,56 +2791,59 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>293400</v>
+      </c>
+      <c r="E43" s="3">
         <v>307300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>236200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>199100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>135800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>201600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>147800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>142100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>124600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>134600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>101000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>91600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>66100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>67000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>49000</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>5</v>
       </c>
@@ -2766,8 +2859,11 @@
       <c r="W43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2831,50 +2927,53 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E45" s="3">
         <v>70200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>29500</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3">
         <v>14300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>15100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>35200</v>
       </c>
       <c r="K45" s="3">
         <v>35200</v>
       </c>
       <c r="L45" s="3">
+        <v>35200</v>
+      </c>
+      <c r="M45" s="3">
         <v>37300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>23300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>111300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>90900</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>5</v>
       </c>
@@ -2890,14 +2989,17 @@
       <c r="U45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
+      <c r="V45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2961,56 +3063,59 @@
       <c r="W46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>6010800</v>
+      </c>
+      <c r="E47" s="3">
         <v>5928500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5390900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5416300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4701400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4453200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3826600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4003900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3008600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2790300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2585000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1958400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2099100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1757700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1290300</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3026,56 +3131,59 @@
       <c r="W47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>425600</v>
+      </c>
+      <c r="E48" s="3">
         <v>394900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>366000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>320300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>311200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>292600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>256200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>222200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>194000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>169400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>143500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>120300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>113100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>49400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>49600</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3091,50 +3199,53 @@
       <c r="W48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>551100</v>
+      </c>
+      <c r="E49" s="3">
         <v>558600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>556200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>577000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>585400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>591400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>596000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>618500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>608300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>607600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>612100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>584400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>279200</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3150,14 +3261,17 @@
       <c r="U49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,56 +3403,59 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>373000</v>
+      </c>
+      <c r="E52" s="3">
         <v>444300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>434900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>403600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>439000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>459100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>422300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>335800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>440500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>298700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>256000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>260200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>216800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>137500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>112200</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3351,8 +3471,11 @@
       <c r="W52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,56 +3539,59 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9201400</v>
+      </c>
+      <c r="E54" s="3">
         <v>9065000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8407100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8155600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7507800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7804800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7165100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6973800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7031700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6952400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5402100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4867000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4766400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2708100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2250500</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>5</v>
       </c>
@@ -3481,8 +3607,11 @@
       <c r="W54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,56 +3661,57 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>35200</v>
+      </c>
+      <c r="E57" s="3">
         <v>59800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>27300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>28600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>30000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>29000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>34500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>33100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>49000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>45600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>425900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>57800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>29000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>26200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>24500</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3596,8 +3727,11 @@
       <c r="W57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3661,56 +3795,59 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>256400</v>
+      </c>
+      <c r="E59" s="3">
         <v>255700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>220300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>170600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>154000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>249700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>220900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>211100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>151400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>213200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>180000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>200800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>177700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>80800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>49200</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>5</v>
       </c>
@@ -3726,8 +3863,11 @@
       <c r="W59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3791,56 +3931,59 @@
       <c r="W60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6240000</v>
+      </c>
+      <c r="E61" s="3">
         <v>6063300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5523600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5344600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4716300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4905700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4221200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4006800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4054400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3927900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2106500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1857300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2001500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1623400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1197800</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3856,8 +3999,11 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3921,8 +4067,11 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,56 +4271,59 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6578000</v>
+      </c>
+      <c r="E66" s="3">
         <v>6430100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5840300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5621400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4996700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5294600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4601600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4355500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4455700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4484100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3024700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2285800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2362400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1730400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1271500</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>5</v>
       </c>
@@ -4181,8 +4339,11 @@
       <c r="W66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4378,14 +4546,14 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>1327300</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>1327200</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,56 +4637,59 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3063900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2929900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2763000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2591200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2385300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2179600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1857200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1605900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1419500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1364800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1205100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-888400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-734900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-494000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-462400</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>5</v>
       </c>
@@ -4531,8 +4705,11 @@
       <c r="W72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,56 +4909,59 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2623500</v>
+      </c>
+      <c r="E76" s="3">
         <v>2634900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2566800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2534200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2511100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2510100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2563400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2618300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2576100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2468300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2377400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2581200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2404000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-349600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-348100</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>5</v>
       </c>
@@ -4791,8 +4977,11 @@
       <c r="W76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-133900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-166900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-171800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-206000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-205700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-322400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-251300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-186400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-54700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-159700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-306600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-123400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-287100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>34800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-85600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-44200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-30800</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,56 +5214,57 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E83" s="3">
         <v>26500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>40100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>43300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>47500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>23000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>20900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>17100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>13100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>12000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>10500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3700</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>5</v>
       </c>
@@ -5081,8 +5280,11 @@
       <c r="W83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,56 +5620,59 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>208200</v>
+      </c>
+      <c r="E89" s="3">
         <v>74300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>98900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>43800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-54300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-28500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>51200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-59100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-28000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-440300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>365200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-19900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-123300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-47700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2300</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>5</v>
       </c>
@@ -5471,8 +5688,11 @@
       <c r="W89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,56 +5716,57 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-46500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-38700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-35800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-24900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-30500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-34300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-31200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-52500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-21100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-21800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-16300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4200</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>5</v>
       </c>
@@ -5561,8 +5782,11 @@
       <c r="W91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,56 +5918,59 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-146800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-624900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-777200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-301000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-692200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>117300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1025700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-166000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-190100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-629500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>84300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-199700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-548900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-357800</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>5</v>
       </c>
@@ -5756,8 +5986,11 @@
       <c r="W94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,56 +6284,59 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E100" s="3">
         <v>506300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>148800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>609500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-129000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>669800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>199500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-28900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>55800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1766300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>244000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-176100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1488600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>447500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>817800</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>5</v>
       </c>
@@ -6106,47 +6352,50 @@
       <c r="W100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E101" s="3">
         <v>3700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-11100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2700</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
@@ -6159,8 +6408,8 @@
       <c r="S101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -6171,56 +6420,59 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>171700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-40500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>228500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-121500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-483300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-48700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>362700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1124800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-139200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1139000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-16800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-114400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1170200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-149100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>457700</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>5</v>
       </c>
@@ -6234,6 +6486,9 @@
         <v>5</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AFRM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFRM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="92">
   <si>
     <t>AFRM</t>
   </si>
@@ -656,178 +656,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>589200</v>
+      </c>
+      <c r="E8" s="3">
         <v>536000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>538400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>462300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>413500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>348200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>340000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>298000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>308900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>302300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>303300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>238400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>219200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>214300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>189500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>157500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>141800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>128400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>125200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>82200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>69600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>73100</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -894,8 +901,11 @@
       <c r="X9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -962,8 +972,11 @@
       <c r="X10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,8 +1001,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1056,8 +1070,11 @@
       <c r="X12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,76 +1141,82 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-22400</v>
+      </c>
+      <c r="E14" s="3">
         <v>9200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>33300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-21200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-28000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-15000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-5600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>7600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>20700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>24300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>57200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>55200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>49400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>43700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>33700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>37900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>14200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>22000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1260,8 +1283,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>662700</v>
+      </c>
+      <c r="E17" s="3">
         <v>696800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>710600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>671700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>657300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>658200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>699500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>585500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>586100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>528800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>499500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>404500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>333500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>423700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>216300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>190800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>102400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>209900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>157900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>115200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>110300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-73500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-160800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-172200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-209400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-243800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-310000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-359500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-287500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-277200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-226500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-196200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-166100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-114300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-209400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-26800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-33300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>39400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-81500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-32700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-33000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-40700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-20300</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,144 +1478,151 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E20" s="3">
         <v>27700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>38700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>36500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>103500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>35500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>36000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>72700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>172100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>36800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-140400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-11600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-77800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>29500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>4300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-96000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-141100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-130600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-164000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-159000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-301000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-230600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-187400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-41300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-147500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-295900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-118000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-282100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-23200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-100</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W21" s="3">
         <v>-28600</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1649,120 +1689,126 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-44100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-133000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-167600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-170700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-207300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-206500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-324000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-251400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-204500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-54400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-159500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-306400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-125900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-287100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-26500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>34900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-85500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-30900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-30700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-36400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-19700</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E24" s="3">
         <v>900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-18100</v>
-      </c>
-      <c r="L24" s="3">
-        <v>300</v>
       </c>
       <c r="M24" s="3">
         <v>300</v>
       </c>
       <c r="N24" s="3">
+        <v>300</v>
+      </c>
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>100</v>
       </c>
       <c r="R24" s="3">
         <v>100</v>
@@ -1780,13 +1826,16 @@
         <v>100</v>
       </c>
       <c r="W24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-45100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-133900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-166900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-171800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-206000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-205700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-322400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-251300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-186400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-54700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-159700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-306600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-123400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-287100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-26600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>34800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-85600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-31000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-30800</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-45100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-133900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-166900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-171800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-206000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-205700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-322400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-251300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-186400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-54700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-159700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-306600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-123400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-287100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-26600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>34800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-85600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-44200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-30800</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,144 +2328,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-29300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-27700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-38700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-36500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-103500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-35500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-36000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-72700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-172100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-36800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>140400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>11600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>77800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-29500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-4300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-45100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-133900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-166900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-171800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-206000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-205700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-322400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-251300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-186400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-54700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-159700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-306600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-123400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-287100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-26600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>34800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-85600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-44200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-30800</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-45100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-133900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-166900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-171800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-206000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-205700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-322400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-251300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-186400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-54700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-159700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-306600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-123400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-287100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-26600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>34800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-85600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-44200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-30800</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,59 +2744,60 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1013100</v>
+      </c>
+      <c r="E41" s="3">
         <v>1272800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1036700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1079300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>892000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>972500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1440300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1530100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1255200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2261900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2567400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1439500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1466600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1623700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>520700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>684400</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>5</v>
       </c>
@@ -2726,8 +2813,11 @@
       <c r="X41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2794,59 +2884,62 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>353000</v>
+      </c>
+      <c r="E43" s="3">
         <v>293400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>307300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>236200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>199100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>135800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>201600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>147800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>142100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>124600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>134600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>101000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>91600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>66100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>67000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>49000</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>5</v>
       </c>
@@ -2862,8 +2955,11 @@
       <c r="X43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2930,53 +3026,56 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3">
         <v>25900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>70200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>29500</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3">
         <v>14300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>15100</v>
-      </c>
-      <c r="K45" s="3">
-        <v>35200</v>
       </c>
       <c r="L45" s="3">
         <v>35200</v>
       </c>
       <c r="M45" s="3">
+        <v>35200</v>
+      </c>
+      <c r="N45" s="3">
         <v>37300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>23300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>111300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>90900</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>5</v>
       </c>
@@ -2992,14 +3091,17 @@
       <c r="V45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
+      <c r="W45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3066,59 +3168,62 @@
       <c r="X46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>6530400</v>
+      </c>
+      <c r="E47" s="3">
         <v>6010800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5928500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5390900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5416300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4701400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4453200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3826600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4003900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3008600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2790300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2585000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1958400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2099100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1757700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1290300</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3134,59 +3239,62 @@
       <c r="X47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>449500</v>
+      </c>
+      <c r="E48" s="3">
         <v>425600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>394900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>366000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>320300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>311200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>292600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>256200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>222200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>194000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>169400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>143500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>120300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>113100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>49400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>49600</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3202,53 +3310,56 @@
       <c r="X48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>546900</v>
+      </c>
+      <c r="E49" s="3">
         <v>551100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>558600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>556200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>577000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>585400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>591400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>596000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>618500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>608300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>607600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>612100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>584400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>279200</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3264,14 +3375,17 @@
       <c r="V49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,59 +3523,62 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>311100</v>
+      </c>
+      <c r="E52" s="3">
         <v>373000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>444300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>434900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>403600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>439000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>459100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>422300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>335800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>440500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>298700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>256000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>260200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>216800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>137500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>112200</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3474,8 +3594,11 @@
       <c r="X52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,59 +3665,62 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9519600</v>
+      </c>
+      <c r="E54" s="3">
         <v>9201400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9065000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8407100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8155600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7507800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7804800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7165100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6973800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7031700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6952400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5402100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4867000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4766400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2708100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2250500</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>5</v>
       </c>
@@ -3610,8 +3736,11 @@
       <c r="X54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,59 +3792,60 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E57" s="3">
         <v>35200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>59800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>27300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>28600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>30000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>29000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>34500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>33100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>49000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>45600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>425900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>57800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>29000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>26200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>24500</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3730,8 +3861,11 @@
       <c r="X57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3798,59 +3932,62 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>283100</v>
+      </c>
+      <c r="E59" s="3">
         <v>256400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>255700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>220300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>170600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>154000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>249700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>220900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>211100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>151400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>213200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>180000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>200800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>177700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>80800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>49200</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>5</v>
       </c>
@@ -3866,8 +4003,11 @@
       <c r="X59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3934,59 +4074,62 @@
       <c r="X60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6415200</v>
+      </c>
+      <c r="E61" s="3">
         <v>6240000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6063300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5523600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5344600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4716300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4905700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4221200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4006800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4054400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3927900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2106500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1857300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2001500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1623400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1197800</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4002,8 +4145,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4070,8 +4216,11 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,59 +4429,62 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6787600</v>
+      </c>
+      <c r="E66" s="3">
         <v>6578000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6430100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5840300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5621400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4996700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5294600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4601600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4355500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4455700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4484100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3024700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2285800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2362400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1730400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1271500</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>5</v>
       </c>
@@ -4342,8 +4500,11 @@
       <c r="X66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4549,14 +4717,14 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>1327300</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>1327200</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,59 +4811,62 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3109000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3063900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2929900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2763000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2591200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2385300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2179600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1857200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1605900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1419500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1364800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1205100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-888400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-734900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-494000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-462400</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>5</v>
       </c>
@@ -4708,8 +4882,11 @@
       <c r="X72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,59 +5095,62 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2732000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2623500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2634900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2566800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2534200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2511100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2510100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2563400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2618300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2576100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2468300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2377400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2581200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2404000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-349600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-348100</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>5</v>
       </c>
@@ -4980,8 +5166,11 @@
       <c r="X76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-45100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-133900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-166900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-171800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-206000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-205700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-322400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-251300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-186400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-54700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-159700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-306600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-123400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-287100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-26600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>34800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-85600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-44200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-30800</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,59 +5413,60 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>65400</v>
+      </c>
+      <c r="E83" s="3">
         <v>37000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>26500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>40100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>43300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>47500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>23000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>20900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>17100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>13100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>12000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>10500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3700</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>5</v>
       </c>
@@ -5283,8 +5482,11 @@
       <c r="X83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,59 +5837,62 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>68800</v>
+      </c>
+      <c r="E89" s="3">
         <v>208200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>74300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>98900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>43800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-54300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-28500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>51200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-59100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-28000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-440300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>365200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-19900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-123300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-47700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2300</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>5</v>
       </c>
@@ -5691,8 +5908,11 @@
       <c r="X89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,59 +5937,60 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-38300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-46500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-38700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-35800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-24900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-30500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-34300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-31200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-52500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-21100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-21800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-16300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4200</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>5</v>
       </c>
@@ -5785,8 +6006,11 @@
       <c r="X91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,59 +6148,62 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-537600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-146800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-624900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-777200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-301000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-692200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>117300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1025700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-166000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-190100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-629500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>84300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-199700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-548900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-357800</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>5</v>
       </c>
@@ -5989,8 +6219,11 @@
       <c r="X94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,59 +6530,62 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>146000</v>
+      </c>
+      <c r="E100" s="3">
         <v>112000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>506300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>148800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>609500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-129000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>669800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>199500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-28900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>55800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1766300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>244000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-176100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1488600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>447500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>817800</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>5</v>
       </c>
@@ -6355,50 +6601,53 @@
       <c r="X100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-3300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-11100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>3600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2700</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>5</v>
       </c>
@@ -6411,8 +6660,8 @@
       <c r="T101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
@@ -6423,59 +6672,62 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-324300</v>
+      </c>
+      <c r="E102" s="3">
         <v>171700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-40500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>228500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-121500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-483300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-48700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>362700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1124800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-139200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1139000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-16800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-114400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1170200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-149100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>457700</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>5</v>
       </c>
@@ -6489,6 +6741,9 @@
         <v>5</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AFRM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFRM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
   <si>
     <t>AFRM</t>
   </si>
@@ -656,208 +656,215 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>589200</v>
+        <v>698500</v>
       </c>
       <c r="E8" s="3">
-        <v>536000</v>
+        <v>659200</v>
       </c>
       <c r="F8" s="3">
-        <v>538400</v>
+        <v>576200</v>
       </c>
       <c r="G8" s="3">
-        <v>462300</v>
+        <v>591100</v>
       </c>
       <c r="H8" s="3">
-        <v>413500</v>
+        <v>496500</v>
       </c>
       <c r="I8" s="3">
-        <v>348200</v>
+        <v>445800</v>
       </c>
       <c r="J8" s="3">
+        <v>381000</v>
+      </c>
+      <c r="K8" s="3">
         <v>340000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>298000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>308900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>302300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>303300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>238400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>219200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>214300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>189500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>157500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>141800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>128400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>125200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>82200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>69600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>73100</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
+      <c r="D9" s="3">
+        <v>413400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>349800</v>
+      </c>
+      <c r="F9" s="3">
+        <v>345200</v>
+      </c>
+      <c r="G9" s="3">
+        <v>349300</v>
+      </c>
+      <c r="H9" s="3">
+        <v>284200</v>
+      </c>
+      <c r="I9" s="3">
+        <v>263700</v>
+      </c>
+      <c r="J9" s="3">
+        <v>214100</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
@@ -904,31 +911,34 @@
       <c r="Y9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>285100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>309400</v>
+      </c>
+      <c r="F10" s="3">
+        <v>230900</v>
+      </c>
+      <c r="G10" s="3">
+        <v>241800</v>
+      </c>
+      <c r="H10" s="3">
+        <v>212400</v>
+      </c>
+      <c r="I10" s="3">
+        <v>182100</v>
+      </c>
+      <c r="J10" s="3">
+        <v>166900</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -975,8 +985,11 @@
       <c r="Y10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,31 +1015,32 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>5</v>
+      <c r="D12" s="3">
+        <v>134300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>124200</v>
+      </c>
+      <c r="F12" s="3">
+        <v>124800</v>
+      </c>
+      <c r="G12" s="3">
+        <v>119800</v>
+      </c>
+      <c r="H12" s="3">
+        <v>133000</v>
+      </c>
+      <c r="I12" s="3">
+        <v>152300</v>
+      </c>
+      <c r="J12" s="3">
+        <v>161800</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>5</v>
@@ -1073,8 +1087,11 @@
       <c r="Y12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,102 +1161,108 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-22400</v>
+        <v>-22900</v>
       </c>
       <c r="E14" s="3">
-        <v>9200</v>
+        <v>1300</v>
       </c>
       <c r="F14" s="3">
-        <v>1000</v>
+        <v>5200</v>
       </c>
       <c r="G14" s="3">
-        <v>2200</v>
+        <v>6400</v>
       </c>
       <c r="H14" s="3">
-        <v>3600</v>
+        <v>2400</v>
       </c>
       <c r="I14" s="3">
-        <v>33300</v>
+        <v>-87600</v>
       </c>
       <c r="J14" s="3">
+        <v>34900</v>
+      </c>
+      <c r="K14" s="3">
         <v>-21200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-28000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-15000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-5600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>7600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>20700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>24300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>57200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>55200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>49400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>43700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>33700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>37900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>14200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>22000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>61000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>79500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>52900</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>48100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>61700</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>64600</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>68600</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1286,8 +1309,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1336,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>662700</v>
+        <v>831400</v>
       </c>
       <c r="E17" s="3">
-        <v>696800</v>
+        <v>732800</v>
       </c>
       <c r="F17" s="3">
-        <v>710600</v>
+        <v>731700</v>
       </c>
       <c r="G17" s="3">
-        <v>671700</v>
+        <v>761400</v>
       </c>
       <c r="H17" s="3">
-        <v>657300</v>
+        <v>703600</v>
       </c>
       <c r="I17" s="3">
-        <v>658200</v>
+        <v>687400</v>
       </c>
       <c r="J17" s="3">
+        <v>656100</v>
+      </c>
+      <c r="K17" s="3">
         <v>699500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>585500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>586100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>528800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>499500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>404500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>333500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>423700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>216300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>190800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>102400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>209900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>157900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>115200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>110300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-73500</v>
+        <v>-132900</v>
       </c>
       <c r="E18" s="3">
-        <v>-160800</v>
+        <v>-73700</v>
       </c>
       <c r="F18" s="3">
-        <v>-172200</v>
+        <v>-155600</v>
       </c>
       <c r="G18" s="3">
+        <v>-170300</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-207000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-241500</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-275100</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-359500</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-287500</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-277200</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-226500</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-196200</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-166100</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-114300</v>
+      </c>
+      <c r="R18" s="3">
         <v>-209400</v>
       </c>
-      <c r="H18" s="3">
-        <v>-243800</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-310000</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-359500</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-287500</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-277200</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-226500</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-196200</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-166100</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-114300</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-209400</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-26800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-33300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>39400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-81500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-32700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-33000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-40700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-20300</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,173 +1512,180 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>29300</v>
+        <v>-12500</v>
       </c>
       <c r="E20" s="3">
-        <v>27700</v>
+        <v>-31600</v>
       </c>
       <c r="F20" s="3">
-        <v>4600</v>
+        <v>-28600</v>
       </c>
       <c r="G20" s="3">
-        <v>38700</v>
+        <v>12700</v>
       </c>
       <c r="H20" s="3">
-        <v>36500</v>
+        <v>-39600</v>
       </c>
       <c r="I20" s="3">
-        <v>103500</v>
+        <v>52500</v>
       </c>
       <c r="J20" s="3">
+        <v>-104500</v>
+      </c>
+      <c r="K20" s="3">
         <v>35500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>36000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>72700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>172100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>36800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-140400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-77800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>29500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-4000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>4300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>21300</v>
+        <v>-59400</v>
       </c>
       <c r="E21" s="3">
-        <v>-96000</v>
+        <v>37400</v>
       </c>
       <c r="F21" s="3">
-        <v>-141100</v>
+        <v>-74100</v>
       </c>
       <c r="G21" s="3">
-        <v>-130600</v>
+        <v>-134900</v>
       </c>
       <c r="H21" s="3">
-        <v>-164000</v>
+        <v>-105700</v>
       </c>
       <c r="I21" s="3">
-        <v>-159000</v>
+        <v>-229400</v>
       </c>
       <c r="J21" s="3">
+        <v>-102000</v>
+      </c>
+      <c r="K21" s="3">
         <v>-301000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-230600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-187400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-41300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-147500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-295900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-118000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-282100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-23200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-100</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3">
         <v>-28600</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1692,126 +1732,132 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-98300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-44100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-133000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-167600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-170700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-207300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-206500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-324000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-251400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-204500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-54400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-159500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-306400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-125900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-287100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-26500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>34900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-85500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-30900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-30700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-36400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-19700</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E24" s="3">
         <v>1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-18100</v>
-      </c>
-      <c r="M24" s="3">
-        <v>300</v>
       </c>
       <c r="N24" s="3">
         <v>300</v>
       </c>
       <c r="O24" s="3">
+        <v>300</v>
+      </c>
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
-      </c>
-      <c r="R24" s="3">
-        <v>100</v>
       </c>
       <c r="S24" s="3">
         <v>100</v>
@@ -1829,13 +1875,16 @@
         <v>100</v>
       </c>
       <c r="X24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-100200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-45100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-133900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-166900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-171800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-206000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-205700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-322400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-251300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-186400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-54700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-159700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-306600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-123400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-287100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-26600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>34800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-85600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-31000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-30800</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-100200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-45100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-133900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-166900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-171800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-206000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-205700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-322400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-251300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-186400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-54700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-159700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-306600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-123400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-287100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-26600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>34800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-85600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-44200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-30800</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,150 +2398,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-29300</v>
+        <v>12500</v>
       </c>
       <c r="E32" s="3">
-        <v>-27700</v>
+        <v>31600</v>
       </c>
       <c r="F32" s="3">
-        <v>-4600</v>
+        <v>28600</v>
       </c>
       <c r="G32" s="3">
-        <v>-38700</v>
+        <v>-12700</v>
       </c>
       <c r="H32" s="3">
-        <v>-36500</v>
+        <v>39600</v>
       </c>
       <c r="I32" s="3">
-        <v>-103500</v>
+        <v>-52500</v>
       </c>
       <c r="J32" s="3">
+        <v>104500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-35500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-36000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-72700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-172100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-36800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>140400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>11600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>77800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-29500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>4000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-100200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-45100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-133900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-166900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-171800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-206000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-205700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-322400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-251300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-186400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-54700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-159700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-306600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-123400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-287100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-26600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>34800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-85600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-44200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-30800</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-100200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-45100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-133900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-166900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-171800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-206000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-205700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-322400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-251300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-186400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-54700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-159700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-306600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-123400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-287100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-26600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>34800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-85600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-44200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-30800</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,62 +2831,63 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1046200</v>
+      </c>
+      <c r="E41" s="3">
         <v>1013100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1272800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1036700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1079300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>892000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>972500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1440300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1530100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1255200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2261900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2567400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1439500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1466600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1623700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>520700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>684400</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>5</v>
       </c>
@@ -2816,31 +2903,34 @@
       <c r="Y41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>848600</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>69700</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>582700</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>685400</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>86500</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>97200</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>145500</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2887,62 +2977,65 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>353000</v>
+        <v>325000</v>
       </c>
       <c r="E43" s="3">
-        <v>293400</v>
+        <v>371300</v>
       </c>
       <c r="F43" s="3">
+        <v>312700</v>
+      </c>
+      <c r="G43" s="3">
         <v>307300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>236200</v>
       </c>
-      <c r="H43" s="3">
-        <v>199100</v>
-      </c>
       <c r="I43" s="3">
+        <v>216300</v>
+      </c>
+      <c r="J43" s="3">
         <v>135800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>201600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>147800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>142100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>124600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>134600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>101000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>91600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>66100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>67000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>49000</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>5</v>
       </c>
@@ -2958,31 +3051,34 @@
       <c r="Y43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3029,22 +3125,25 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E45" s="3">
-        <v>25900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>70200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>29500</v>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>5</v>
@@ -3052,33 +3151,33 @@
       <c r="I45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K45" s="3">
         <v>14300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15100</v>
-      </c>
-      <c r="L45" s="3">
-        <v>35200</v>
       </c>
       <c r="M45" s="3">
         <v>35200</v>
       </c>
       <c r="N45" s="3">
+        <v>35200</v>
+      </c>
+      <c r="O45" s="3">
         <v>37300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>23300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>111300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>90900</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>5</v>
       </c>
@@ -3094,37 +3193,40 @@
       <c r="W45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X45" s="3">
-        <v>0</v>
+      <c r="X45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>2613400</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>1786600</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>2567000</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>2543900</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>1866400</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>1623500</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>1692800</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -3171,62 +3273,65 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>6530400</v>
+        <v>6249700</v>
       </c>
       <c r="E47" s="3">
-        <v>6010800</v>
+        <v>6513100</v>
       </c>
       <c r="F47" s="3">
-        <v>5928500</v>
+        <v>5444100</v>
       </c>
       <c r="G47" s="3">
-        <v>5390900</v>
+        <v>5290900</v>
       </c>
       <c r="H47" s="3">
-        <v>5416300</v>
+        <v>5304400</v>
       </c>
       <c r="I47" s="3">
-        <v>4701400</v>
+        <v>5369600</v>
       </c>
       <c r="J47" s="3">
+        <v>4605300</v>
+      </c>
+      <c r="K47" s="3">
         <v>4453200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3826600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4003900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3008600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2790300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2585000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1958400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2099100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1757700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1290300</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3242,62 +3347,65 @@
       <c r="Y47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>492700</v>
+      </c>
+      <c r="E48" s="3">
         <v>449500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>425600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>394900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>366000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>320300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>311200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>292600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>256200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>222200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>194000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>169400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>143500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>120300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>113100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>49400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>49600</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3313,56 +3421,59 @@
       <c r="Y48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>550200</v>
+      </c>
+      <c r="E49" s="3">
         <v>546900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>551100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>558600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>556200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>577000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>585400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>591400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>596000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>618500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>608300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>607600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>612100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>584400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>279200</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3378,14 +3489,17 @@
       <c r="W49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,62 +3643,65 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>311100</v>
+        <v>212900</v>
       </c>
       <c r="E52" s="3">
-        <v>373000</v>
+        <v>202200</v>
       </c>
       <c r="F52" s="3">
-        <v>444300</v>
+        <v>192400</v>
       </c>
       <c r="G52" s="3">
-        <v>434900</v>
+        <v>254000</v>
       </c>
       <c r="H52" s="3">
-        <v>403600</v>
+        <v>314200</v>
       </c>
       <c r="I52" s="3">
-        <v>439000</v>
+        <v>242000</v>
       </c>
       <c r="J52" s="3">
+        <v>313100</v>
+      </c>
+      <c r="K52" s="3">
         <v>459100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>422300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>335800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>440500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>298700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>256000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>260200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>216800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>137500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>112200</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3597,8 +3717,11 @@
       <c r="Y52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,62 +3791,65 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10139200</v>
+      </c>
+      <c r="E54" s="3">
         <v>9519600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9201400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9065000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8407100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8155600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7507800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7804800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7165100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6973800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7031700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6952400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5402100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4867000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4766400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2708100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2250500</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>5</v>
       </c>
@@ -3739,8 +3865,11 @@
       <c r="Y54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,62 +3923,63 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>57600</v>
+      </c>
+      <c r="E57" s="3">
         <v>41000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>35200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>59800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>27300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>28600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>30000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>29000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>34500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>33100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>49000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>45600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>425900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>57800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>29000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>26200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>24500</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3864,22 +3995,25 @@
       <c r="Y57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>12600</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>16700</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -3935,62 +4069,65 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>283100</v>
+      <c r="D59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E59" s="3">
-        <v>256400</v>
+        <v>17600</v>
       </c>
       <c r="F59" s="3">
-        <v>255700</v>
+        <v>21200</v>
       </c>
       <c r="G59" s="3">
-        <v>220300</v>
-      </c>
-      <c r="H59" s="3">
-        <v>170600</v>
+        <v>23300</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I59" s="3">
-        <v>154000</v>
-      </c>
-      <c r="J59" s="3">
+        <v>53300</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K59" s="3">
         <v>249700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>220900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>211100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>151400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>213200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>180000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>200800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>177700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>80800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>49200</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4006,31 +4143,34 @@
       <c r="Y59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>148700</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>159300</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>144100</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>168900</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>89100</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>146100</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>83800</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -4077,62 +4217,65 @@
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>6415200</v>
+        <v>7107300</v>
       </c>
       <c r="E61" s="3">
-        <v>6240000</v>
+        <v>6597600</v>
       </c>
       <c r="F61" s="3">
-        <v>6063300</v>
+        <v>6408700</v>
       </c>
       <c r="G61" s="3">
-        <v>5523600</v>
+        <v>6233200</v>
       </c>
       <c r="H61" s="3">
-        <v>5344600</v>
+        <v>5682200</v>
       </c>
       <c r="I61" s="3">
-        <v>4716300</v>
+        <v>5451000</v>
       </c>
       <c r="J61" s="3">
+        <v>4816500</v>
+      </c>
+      <c r="K61" s="3">
         <v>4905700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4221200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4006800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4054400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3927900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2106500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1857300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2001500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1623400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1197800</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4148,31 +4291,34 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>47600</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>30700</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>25100</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>69100</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>24400</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>96400</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -4219,8 +4365,11 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,62 +4587,65 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7303600</v>
+      </c>
+      <c r="E66" s="3">
         <v>6787600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6578000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6430100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5840300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5621400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4996700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5294600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4601600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4355500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4455700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4484100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3024700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2285800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2362400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1730400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1271500</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>5</v>
       </c>
@@ -4503,8 +4661,11 @@
       <c r="Y66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4720,14 +4888,14 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>1327300</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>1327200</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,62 +4985,65 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3209200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3109000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3063900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2929900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2763000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2591200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2385300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2179600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1857200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1605900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1419500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1364800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1205100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-888400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-734900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-494000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-462400</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>5</v>
       </c>
@@ -4885,8 +5059,11 @@
       <c r="Y72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,62 +5281,65 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2835600</v>
+      </c>
+      <c r="E76" s="3">
         <v>2732000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2623500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2634900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2566800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2534200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2511100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2510100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2563400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2618300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2576100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2468300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2377400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2581200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2404000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-349600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-348100</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>5</v>
       </c>
@@ -5169,8 +5355,11 @@
       <c r="Y76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-100200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-45100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-133900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-166900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-171800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-206000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-205700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-322400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-251300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-186400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-54700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-159700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-306600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-123400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-287100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-26600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>34800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-85600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-44200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-30800</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,62 +5612,63 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>65400</v>
+        <v>25900</v>
       </c>
       <c r="E83" s="3">
-        <v>37000</v>
+        <v>29200</v>
       </c>
       <c r="F83" s="3">
-        <v>26500</v>
+        <v>23900</v>
       </c>
       <c r="G83" s="3">
-        <v>40100</v>
+        <v>8200</v>
       </c>
       <c r="H83" s="3">
-        <v>43300</v>
+        <v>20900</v>
       </c>
       <c r="I83" s="3">
-        <v>47500</v>
+        <v>10000</v>
       </c>
       <c r="J83" s="3">
+        <v>7700</v>
+      </c>
+      <c r="K83" s="3">
         <v>23000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>20900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>17100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>10500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3700</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>5</v>
       </c>
@@ -5485,8 +5684,11 @@
       <c r="Y83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,62 +6054,65 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>196900</v>
+      </c>
+      <c r="E89" s="3">
         <v>68800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>208200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>74300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>98900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>43800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-54300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-28500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>51200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-59100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-28000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-440300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>365200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-19900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-123300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-47700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2300</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>5</v>
       </c>
@@ -5911,8 +6128,11 @@
       <c r="Y89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,62 +6158,63 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-44200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-38300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-46500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-38700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-35800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-24900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-30500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-34300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-31200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-52500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-21100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-21800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-16300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4200</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>5</v>
       </c>
@@ -6009,8 +6230,11 @@
       <c r="Y91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,62 +6378,65 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-575000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-537600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-146800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-624900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-777200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-301000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-692200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>117300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1025700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-166000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-190100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-629500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>84300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-199700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-548900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-357800</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>5</v>
       </c>
@@ -6222,8 +6452,11 @@
       <c r="Y94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,31 +6482,32 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,62 +6776,65 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>465600</v>
+      </c>
+      <c r="E100" s="3">
         <v>146000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>112000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>506300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>148800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>609500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-129000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>669800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>199500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-28900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>55800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1766300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>244000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-176100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1488600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>447500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>817800</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>5</v>
       </c>
@@ -6604,53 +6850,56 @@
       <c r="Y100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-1400</v>
+        <v>-3300</v>
       </c>
       <c r="E101" s="3">
-        <v>-1700</v>
+        <v>2300</v>
       </c>
       <c r="F101" s="3">
-        <v>3700</v>
+        <v>900</v>
       </c>
       <c r="G101" s="3">
-        <v>-3300</v>
+        <v>2200</v>
       </c>
       <c r="H101" s="3">
-        <v>2300</v>
+        <v>-5300</v>
       </c>
       <c r="I101" s="3">
-        <v>900</v>
+        <v>-11100</v>
       </c>
       <c r="J101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K101" s="3">
         <v>2200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-11100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>5</v>
       </c>
@@ -6663,8 +6912,8 @@
       <c r="U101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="V101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
@@ -6675,62 +6924,65 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>89200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-324300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>171700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-40500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>228500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-121500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-483300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-48700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>362700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1124800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-139200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1139000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-16800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-114400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1170200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-149100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>457700</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>5</v>
       </c>
@@ -6744,6 +6996,9 @@
         <v>5</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AFRM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFRM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
   <si>
     <t>AFRM</t>
   </si>
@@ -656,219 +656,225 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>866400</v>
+      </c>
+      <c r="E8" s="3">
         <v>698500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>659200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>576200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>591100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>496500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>445800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>381000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>340000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>298000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>308900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>302300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>303300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>238400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>219200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>214300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>189500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>157500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>141800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>128400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>125200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>82200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>69600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>73100</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>447000</v>
+      </c>
+      <c r="E9" s="3">
         <v>413400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>349800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>345200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>349300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>284200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>263700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>214100</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
@@ -914,35 +920,38 @@
       <c r="Z9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>419400</v>
+      </c>
+      <c r="E10" s="3">
         <v>285100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>309400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>230900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>241800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>212400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>182100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>166900</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -988,8 +997,11 @@
       <c r="Z10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,35 +1028,36 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>148200</v>
+      </c>
+      <c r="E12" s="3">
         <v>134300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>124200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>124800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>119800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>133000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>152300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>161800</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>5</v>
       </c>
@@ -1090,8 +1103,11 @@
       <c r="Z12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,109 +1180,115 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-82400</v>
+      </c>
+      <c r="E14" s="3">
         <v>-22900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5200</v>
       </c>
-      <c r="G14" s="3">
-        <v>6400</v>
-      </c>
       <c r="H14" s="3">
+        <v>15200</v>
+      </c>
+      <c r="I14" s="3">
         <v>2400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-87600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>34900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-21200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-28000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-15000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-5600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>7600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>20700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>24300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>57200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>55200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>49400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>43700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>33700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>37900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>14200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>22000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>69100</v>
+      </c>
+      <c r="E15" s="3">
         <v>61000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>79500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>52900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>48100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>61700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>64600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>68600</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1312,8 +1334,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>870600</v>
+      </c>
+      <c r="E17" s="3">
         <v>831400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>732800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>731700</v>
       </c>
-      <c r="G17" s="3">
-        <v>761400</v>
-      </c>
       <c r="H17" s="3">
+        <v>762200</v>
+      </c>
+      <c r="I17" s="3">
         <v>703600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>687400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>656100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>699500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>585500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>586100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>528800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>499500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>404500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>333500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>423700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>216300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>190800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>102400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>209900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>157900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>115200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>110300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-132900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-73700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-155600</v>
       </c>
-      <c r="G18" s="3">
-        <v>-170300</v>
-      </c>
       <c r="H18" s="3">
+        <v>-171100</v>
+      </c>
+      <c r="I18" s="3">
         <v>-207000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-241500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-275100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-359500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-287500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-277200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-226500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-196200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-166100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-114300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-209400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-26800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-33300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>39400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-81500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-32700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-33000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-40700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-20300</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,167 +1545,174 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-12500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-31600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-28600</v>
       </c>
-      <c r="G20" s="3">
-        <v>12700</v>
-      </c>
       <c r="H20" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="I20" s="3">
         <v>-39600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>52500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-104500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>35500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>36000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>72700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>172100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>36800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-140400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-11600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-77800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>29500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-4500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-4000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>4300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>70600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-59400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>37400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-74100</v>
       </c>
-      <c r="G21" s="3">
-        <v>-134900</v>
-      </c>
       <c r="H21" s="3">
+        <v>-103500</v>
+      </c>
+      <c r="I21" s="3">
         <v>-105700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-229400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-102000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-301000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-230600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-187400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-41300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-147500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-295900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-118000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-282100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-23200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-100</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-28600</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E22" s="3">
         <v>800</v>
       </c>
       <c r="F22" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="G22" s="3">
         <v>900</v>
@@ -1682,14 +1721,14 @@
         <v>900</v>
       </c>
       <c r="I22" s="3">
+        <v>900</v>
+      </c>
+      <c r="J22" s="3">
         <v>800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1000</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -1735,132 +1774,138 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>82900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-98300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-44100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-133000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-167600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-170700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-207300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-206500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-324000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-251400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-204500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-54400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-159500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-306400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-125900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-287100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-26500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>34900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-85500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-30900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-30700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-36400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-19700</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E24" s="3">
         <v>1900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-18100</v>
-      </c>
-      <c r="N24" s="3">
-        <v>300</v>
       </c>
       <c r="O24" s="3">
         <v>300</v>
       </c>
       <c r="P24" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
-      </c>
-      <c r="S24" s="3">
-        <v>100</v>
       </c>
       <c r="T24" s="3">
         <v>100</v>
@@ -1878,13 +1923,16 @@
         <v>100</v>
       </c>
       <c r="Y24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>80400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-100200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-45100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-133900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-166900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-171800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-206000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-205700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-322400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-251300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-186400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-54700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-159700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-306600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-123400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-287100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-26600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>34800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-85600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-31000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-30800</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>80400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-100200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-45100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-133900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-166900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-171800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-206000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-205700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-322400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-251300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-186400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-54700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-159700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-306600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-123400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-287100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-26600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>34800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-85600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-44200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-30800</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,156 +2467,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E32" s="3">
         <v>12500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>31600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>28600</v>
       </c>
-      <c r="G32" s="3">
-        <v>-12700</v>
-      </c>
       <c r="H32" s="3">
+        <v>19500</v>
+      </c>
+      <c r="I32" s="3">
         <v>39600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-52500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>104500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-35500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-36000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-72700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-172100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-36800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>140400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>11600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>77800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-29500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>4500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>4000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>80400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-100200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-45100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-133900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-166900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-171800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-206000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-205700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-322400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-251300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-186400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-54700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-159700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-306600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-123400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-287100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-26600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>34800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-85600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-44200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-30800</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>80400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-100200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-45100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-133900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-166900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-171800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-206000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-205700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-322400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-251300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-186400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-54700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-159700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-306600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-123400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-287100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-26600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>34800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-85600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-44200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-30800</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,65 +2917,66 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1200400</v>
+      </c>
+      <c r="E41" s="3">
         <v>1046200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1013100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1272800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1036700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1079300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>892000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>972500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1440300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1530100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1255200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2261900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2567400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1439500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1466600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1623700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>520700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>684400</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>5</v>
       </c>
@@ -2906,35 +2992,38 @@
       <c r="Z41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E42" s="3">
         <v>848600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>69700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>582700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>685400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>86500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>97200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>145500</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2980,65 +3069,68 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>216800</v>
+      </c>
+      <c r="E43" s="3">
         <v>325000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>371300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>312700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>307300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>236200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>216300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>135800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>201600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>147800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>142100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>124600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>134600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>101000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>91600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>66100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>67000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>49000</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>5</v>
       </c>
@@ -3054,8 +3146,11 @@
       <c r="Z43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3080,8 +3175,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3128,8 +3223,11 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3154,33 +3252,33 @@
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L45" s="3">
         <v>14300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>15100</v>
-      </c>
-      <c r="M45" s="3">
-        <v>35200</v>
       </c>
       <c r="N45" s="3">
         <v>35200</v>
       </c>
       <c r="O45" s="3">
+        <v>35200</v>
+      </c>
+      <c r="P45" s="3">
         <v>37300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>23300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>111300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>90900</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>5</v>
       </c>
@@ -3196,41 +3294,44 @@
       <c r="X45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y45" s="3">
-        <v>0</v>
+      <c r="Y45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2049900</v>
+      </c>
+      <c r="E46" s="3">
         <v>2613400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1786600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2567000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2543900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1866400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1623500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1692800</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -3276,65 +3377,68 @@
       <c r="Z46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7131300</v>
+      </c>
+      <c r="E47" s="3">
         <v>6249700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6513100</v>
       </c>
-      <c r="F47" s="3">
-        <v>5444100</v>
-      </c>
       <c r="G47" s="3">
+        <v>5465600</v>
+      </c>
+      <c r="H47" s="3">
         <v>5290900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5304400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5369600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4605300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4453200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3826600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4003900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3008600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2790300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2585000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1958400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2099100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1757700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1290300</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3350,65 +3454,68 @@
       <c r="Z47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>523800</v>
+      </c>
+      <c r="E48" s="3">
         <v>492700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>449500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>425600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>394900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>366000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>320300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>311200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>292600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>256200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>222200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>194000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>169400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>143500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>120300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>113100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>49400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>49600</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3424,59 +3531,62 @@
       <c r="Z48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>533900</v>
+      </c>
+      <c r="E49" s="3">
         <v>550200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>546900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>551100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>558600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>556200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>577000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>585400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>591400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>596000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>618500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>608300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>607600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>612100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>584400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>279200</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3492,14 +3602,17 @@
       <c r="X49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
+      <c r="Y49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,65 +3762,68 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>224300</v>
+      </c>
+      <c r="E52" s="3">
         <v>212900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>202200</v>
       </c>
-      <c r="F52" s="3">
-        <v>192400</v>
-      </c>
       <c r="G52" s="3">
+        <v>171000</v>
+      </c>
+      <c r="H52" s="3">
         <v>254000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>314200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>242000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>313100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>459100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>422300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>335800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>440500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>298700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>256000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>260200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>216800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>137500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>112200</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3720,8 +3839,11 @@
       <c r="Z52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,65 +3916,68 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10481100</v>
+      </c>
+      <c r="E54" s="3">
         <v>10139200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9519600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9201400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9065000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8407100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8155600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7507800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7804800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7165100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6973800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7031700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6952400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5402100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4867000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4766400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2708100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2250500</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>5</v>
       </c>
@@ -3868,8 +3993,11 @@
       <c r="Z54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,65 +4053,66 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>50600</v>
+      </c>
+      <c r="E57" s="3">
         <v>57600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>41000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>35200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>59800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>27300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>28600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>30000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>29000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>34500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>33100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>49000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>45600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>425900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>57800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>29000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>26200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>24500</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3998,26 +4128,29 @@
       <c r="Z57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E58" s="3">
         <v>12600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>16700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10200</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
@@ -4072,65 +4205,68 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E59" s="3">
+      <c r="D59" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3">
         <v>17600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>21200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>23300</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3">
         <v>53300</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L59" s="3">
         <v>249700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>220900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>211100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>151400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>213200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>180000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>200800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>177700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>80800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>49200</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4146,35 +4282,38 @@
       <c r="Z59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>166800</v>
+      </c>
+      <c r="E60" s="3">
         <v>148700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>159300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>144100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>168900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>89100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>146100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>83800</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -4220,65 +4359,68 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7487600</v>
+      </c>
+      <c r="E61" s="3">
         <v>7107300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6597600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6408700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6233200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5682200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5451000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4816500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4905700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4221200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4006800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4054400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3927900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2106500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1857300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2001500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1623400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1197800</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4294,35 +4436,38 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E62" s="3">
         <v>47600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>30700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>25100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>28000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>69100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>24400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>96400</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -4368,8 +4513,11 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,65 +4744,68 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7695500</v>
+      </c>
+      <c r="E66" s="3">
         <v>7303600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6787600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6578000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6430100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5840300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5621400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4996700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5294600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4601600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4355500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4455700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4484100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3024700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2285800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2362400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1730400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1271500</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>5</v>
       </c>
@@ -4664,8 +4821,11 @@
       <c r="Z66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4891,14 +5058,14 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>1327300</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>1327200</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -4914,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,65 +5158,68 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3128900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3209200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3109000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-3063900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2929900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2763000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2591200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2385300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2179600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1857200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1605900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1419500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1364800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1205100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-888400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-734900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-494000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-462400</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>5</v>
       </c>
@@ -5062,8 +5235,11 @@
       <c r="Z72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,65 +5466,68 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2785500</v>
+      </c>
+      <c r="E76" s="3">
         <v>2835600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2732000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2623500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2634900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2566800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2534200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2511100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2510100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2563400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2618300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2576100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2468300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2377400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2581200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2404000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-349600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-348100</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>5</v>
       </c>
@@ -5358,8 +5543,11 @@
       <c r="Z76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>80400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-100200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-45100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-133900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-166900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-171800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-206000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-205700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-322400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-251300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-186400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-54700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-159700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-306600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-123400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-287100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-26600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>34800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-85600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-44200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-30800</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,65 +5810,66 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E83" s="3">
         <v>25900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>29200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>23900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>20900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>10000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>23000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>20900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>17100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>12000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>10500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3700</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>5</v>
       </c>
@@ -5687,8 +5885,11 @@
       <c r="Z83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,65 +6270,68 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>312000</v>
+      </c>
+      <c r="E89" s="3">
         <v>196900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>68800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>208200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>74300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>98900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>43800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-54300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-28500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>51200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-59100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-28000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-440300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>365200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-19900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-123300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-47700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2300</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>5</v>
       </c>
@@ -6131,8 +6347,11 @@
       <c r="Z89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,65 +6378,66 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-44200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-38300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-46500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-38700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-35800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-24900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-30500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-34300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-31200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-52500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-21100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-21800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-16300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4200</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>5</v>
       </c>
@@ -6233,8 +6453,11 @@
       <c r="Z91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,65 +6607,68 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-89100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-575000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-537600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-146800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-624900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-15900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-777200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-301000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-692200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>117300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1025700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-166000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-190100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-629500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>84300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-199700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-548900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-357800</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>5</v>
       </c>
@@ -6455,8 +6684,11 @@
       <c r="Z94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6509,8 +6742,8 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6557,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,65 +7021,68 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>144100</v>
+      </c>
+      <c r="E100" s="3">
         <v>465600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>146000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>112000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>506300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>148800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>609500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-129000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>669800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>199500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-28900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>55800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1766300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>244000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-176100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1488600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>447500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>817800</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>5</v>
       </c>
@@ -6853,56 +7098,59 @@
       <c r="Z100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-3300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-11100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-11100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2700</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>5</v>
       </c>
@@ -6915,8 +7163,8 @@
       <c r="V101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
+      <c r="W101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
@@ -6927,65 +7175,68 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>352500</v>
+      </c>
+      <c r="E102" s="3">
         <v>89200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-324300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>171700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-40500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>228500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-121500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-483300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-48700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>362700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1124800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-139200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1139000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-114400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1170200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-149100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>457700</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>5</v>
       </c>
@@ -6999,6 +7250,9 @@
         <v>5</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AFRM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFRM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
   <si>
     <t>AFRM</t>
   </si>
@@ -656,228 +656,235 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>783100</v>
+      </c>
+      <c r="E8" s="3">
         <v>866400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>698500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>659200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>576200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>591100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>496500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>445800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>381000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>340000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>298000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>308900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>302300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>303300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>238400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>219200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>214300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>189500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>157500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>141800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>128400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>125200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>82200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>69600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>73100</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>430600</v>
+      </c>
+      <c r="E9" s="3">
         <v>447000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>413400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>349800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>345200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>349300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>284200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>263700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>214100</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
@@ -923,38 +930,41 @@
       <c r="AA9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>352600</v>
+      </c>
+      <c r="E10" s="3">
         <v>419400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>285100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>309400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>230900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>241800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>212400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>182100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>166900</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1000,8 +1010,11 @@
       <c r="AA10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1029,38 +1042,39 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>152600</v>
+      </c>
+      <c r="E12" s="3">
         <v>148200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>134300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>124200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>124800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>119800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>133000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>152300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>161800</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>5</v>
       </c>
@@ -1106,8 +1120,11 @@
       <c r="AA12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,115 +1200,121 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-82400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-22900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>5200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>15200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-87600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>34900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-21200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-28000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-15000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-5600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>7600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>20700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>24300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>57200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>55200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>49400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>43700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>33700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>37900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>14200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>22000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>70400</v>
+      </c>
+      <c r="E15" s="3">
         <v>69100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>61000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>79500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>52900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>48100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>61700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>64600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>68600</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1337,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>791500</v>
+      </c>
+      <c r="E17" s="3">
         <v>870600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>831400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>732800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>731700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>762200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>703600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>687400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>656100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>699500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>585500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>586100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>528800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>499500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>404500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>333500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>423700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>216300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>190800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>102400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>209900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>157900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>115200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>110300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-132900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-73700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-155600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-171100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-207000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-241500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-275100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-359500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-287500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-277200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-226500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-196200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-166100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-114300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-209400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-26800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-33300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>39400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-81500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-32700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-33000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-40700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-20300</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,176 +1579,183 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-12500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-31600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-28600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-19500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-39600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>52500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-104500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>35500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>36000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>72700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>172100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>36800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-140400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-11600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-77800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>29500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-4500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-4000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>4300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>78300</v>
+      </c>
+      <c r="E21" s="3">
         <v>70600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-59400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>37400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-74100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-103500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-105700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-229400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-102000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-301000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-230600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-187400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-41300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-147500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-295900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-118000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-282100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-23200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-100</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-28600</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E22" s="3">
         <v>1000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>800</v>
       </c>
       <c r="F22" s="3">
         <v>800</v>
       </c>
       <c r="G22" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="H22" s="3">
         <v>900</v>
@@ -1724,14 +1764,14 @@
         <v>900</v>
       </c>
       <c r="J22" s="3">
+        <v>900</v>
+      </c>
+      <c r="K22" s="3">
         <v>800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1000</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1777,85 +1817,91 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E23" s="3">
         <v>82900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-98300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-44100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-133000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-167600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-170700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-207300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-206500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-324000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-251400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-204500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-54400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-159500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-306400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-125900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-287100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-26500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>34900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-85500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-30900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-30700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-36400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-19700</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1863,52 +1909,52 @@
         <v>2500</v>
       </c>
       <c r="E24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F24" s="3">
         <v>1900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-18100</v>
-      </c>
-      <c r="O24" s="3">
-        <v>300</v>
       </c>
       <c r="P24" s="3">
         <v>300</v>
       </c>
       <c r="Q24" s="3">
+        <v>300</v>
+      </c>
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-2400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-100</v>
-      </c>
-      <c r="T24" s="3">
-        <v>100</v>
       </c>
       <c r="U24" s="3">
         <v>100</v>
@@ -1926,13 +1972,16 @@
         <v>100</v>
       </c>
       <c r="Z24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E26" s="3">
         <v>80400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-100200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-45100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-133900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-166900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-171800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-206000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-205700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-322400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-251300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-186400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-54700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-159700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-306600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-123400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-287100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-26600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>34800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-85600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-31000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-30800</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E27" s="3">
         <v>80400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-100200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-45100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-133900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-166900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-171800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-206000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-205700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-322400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-251300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-186400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-54700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-159700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-306600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-123400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-287100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-26600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>34800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-85600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-44200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-30800</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2316,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,162 +2537,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E32" s="3">
         <v>5800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>12500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>31600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>28600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>19500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>39600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-52500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>104500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-35500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-36000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-72700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-172100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-36800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>140400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>11600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>77800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-29500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>4500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>4000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E33" s="3">
         <v>80400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-100200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-45100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-133900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-166900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-171800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-206000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-205700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-322400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-251300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-186400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-54700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-159700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-306600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-123400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-287100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-26600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>34800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-85600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-44200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-30800</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E35" s="3">
         <v>80400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-100200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-45100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-133900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-166900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-171800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-206000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-205700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-322400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-251300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-186400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-54700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-159700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-306600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-123400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-287100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-26600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>34800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-85600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-44200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-30800</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,68 +3004,69 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1351100</v>
+      </c>
+      <c r="E41" s="3">
         <v>1200400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1046200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1013100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1272800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1036700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1079300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>892000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>972500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1440300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1530100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1255200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2261900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2567400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1439500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1466600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1623700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>520700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>684400</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>5</v>
       </c>
@@ -2995,38 +3082,41 @@
       <c r="AA41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E42" s="3">
         <v>39400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>848600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>69700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>582700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>685400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>86500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>97200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>145500</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3072,68 +3162,71 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>231900</v>
+      </c>
+      <c r="E43" s="3">
         <v>216800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>325000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>371300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>312700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>307300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>236200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>216300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>135800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>201600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>147800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>142100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>124600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>134600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>101000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>91600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>66100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>67000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>49000</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>5</v>
       </c>
@@ -3149,8 +3242,11 @@
       <c r="AA43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3178,8 +3274,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3226,8 +3322,11 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3255,33 +3354,33 @@
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M45" s="3">
         <v>14300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>15100</v>
-      </c>
-      <c r="N45" s="3">
-        <v>35200</v>
       </c>
       <c r="O45" s="3">
         <v>35200</v>
       </c>
       <c r="P45" s="3">
+        <v>35200</v>
+      </c>
+      <c r="Q45" s="3">
         <v>37300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>23300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>111300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>90900</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>5</v>
       </c>
@@ -3297,44 +3396,47 @@
       <c r="Y45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z45" s="3">
-        <v>0</v>
+      <c r="Z45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2053900</v>
+      </c>
+      <c r="E46" s="3">
         <v>2049900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2613400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1786600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2567000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2543900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1866400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1623500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1692800</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -3380,68 +3482,71 @@
       <c r="AA46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7073000</v>
+      </c>
+      <c r="E47" s="3">
         <v>7131300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6249700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6513100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5465600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5290900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5304400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5369600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4605300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4453200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3826600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4003900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3008600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2790300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2585000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1958400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2099100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1757700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1290300</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3457,68 +3562,71 @@
       <c r="AA47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>564800</v>
+      </c>
+      <c r="E48" s="3">
         <v>523800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>492700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>449500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>425600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>394900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>366000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>320300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>311200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>292600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>256200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>222200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>194000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>169400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>143500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>120300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>113100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>49400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>49600</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3534,62 +3642,65 @@
       <c r="AA48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>534800</v>
+      </c>
+      <c r="E49" s="3">
         <v>533900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>550200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>546900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>551100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>558600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>556200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>577000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>585400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>591400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>596000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>618500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>608300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>607600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>612100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>584400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>279200</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3605,14 +3716,17 @@
       <c r="Y49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
+      <c r="Z49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,68 +3882,71 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>194500</v>
+      </c>
+      <c r="E52" s="3">
         <v>224300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>212900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>202200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>171000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>254000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>314200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>242000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>313100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>459100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>422300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>335800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>440500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>298700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>256000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>260200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>216800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>137500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>112200</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3842,8 +3962,11 @@
       <c r="AA52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,68 +4042,71 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10436200</v>
+      </c>
+      <c r="E54" s="3">
         <v>10481100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10139200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9519600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9201400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9065000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8407100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8155600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7507800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7804800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7165100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6973800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7031700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6952400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5402100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4867000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4766400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2708100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2250500</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>5</v>
       </c>
@@ -3996,8 +4122,11 @@
       <c r="AA54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,68 +4184,69 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>41100</v>
+      </c>
+      <c r="E57" s="3">
         <v>50600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>57600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>41000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>35200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>59800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>27300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>28600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>30000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>29000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>34500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>33100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>49000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>45600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>425900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>57800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>29000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>26200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>24500</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>5</v>
       </c>
@@ -4131,29 +4262,32 @@
       <c r="AA57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E58" s="3">
         <v>8400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>16700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10200</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -4208,68 +4342,71 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E59" s="3">
         <v>8200</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3">
         <v>17600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>21200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>23300</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K59" s="3">
         <v>53300</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M59" s="3">
         <v>249700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>220900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>211100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>151400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>213200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>180000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>200800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>177700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>80800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>49200</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4285,38 +4422,41 @@
       <c r="AA59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>152400</v>
+      </c>
+      <c r="E60" s="3">
         <v>166800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>148700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>159300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>144100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>168900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>89100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>146100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>83800</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -4362,68 +4502,71 @@
       <c r="AA60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7354100</v>
+      </c>
+      <c r="E61" s="3">
         <v>7487600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7107300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6597600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6408700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6233200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5682200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5451000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4816500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4905700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4221200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4006800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4054400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3927900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2106500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1857300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2001500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1623400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1197800</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4439,38 +4582,41 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>54800</v>
+      </c>
+      <c r="E62" s="3">
         <v>41200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>47600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>30700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>25100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>28000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>69100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>24400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>96400</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -4516,8 +4662,11 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,68 +4902,71 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7561300</v>
+      </c>
+      <c r="E66" s="3">
         <v>7695500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7303600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6787600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6578000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6430100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5840300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5621400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4996700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5294600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4601600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4355500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4455700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4484100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3024700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2285800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2362400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1730400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1271500</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>5</v>
       </c>
@@ -4824,8 +4982,11 @@
       <c r="AA66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5061,14 +5229,14 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>1327300</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>1327200</v>
       </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,68 +5332,71 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3126100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3128900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3209200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-3109000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3063900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2929900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2763000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2591200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2385300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2179600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1857200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1605900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1419500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1364800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1205100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-888400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-734900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-494000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-462400</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>5</v>
       </c>
@@ -5238,8 +5412,11 @@
       <c r="AA72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,68 +5652,71 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2874900</v>
+      </c>
+      <c r="E76" s="3">
         <v>2785500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2835600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2732000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2623500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2634900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2566800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2534200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2511100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2510100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2563400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2618300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2576100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2468300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2377400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2581200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2404000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-349600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-348100</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>5</v>
       </c>
@@ -5546,8 +5732,11 @@
       <c r="AA76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E81" s="3">
         <v>80400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-100200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-45100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-133900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-166900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-171800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-206000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-205700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-322400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-251300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-186400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-54700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-159700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-306600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-123400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-287100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-26600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>34800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-85600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-44200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-30800</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,68 +6009,69 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E83" s="3">
         <v>23600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>25900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>29200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>23900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>20900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>10000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>23000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>20900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>17100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>12000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>10500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3700</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>5</v>
       </c>
@@ -5888,8 +6087,11 @@
       <c r="AA83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,68 +6487,71 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>210400</v>
+      </c>
+      <c r="E89" s="3">
         <v>312000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>196900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>68800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>208200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>74300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>98900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>43800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-54300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-28500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>51200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-59100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-28000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-440300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>365200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-19900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-123300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-47700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2300</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>5</v>
       </c>
@@ -6350,8 +6567,11 @@
       <c r="AA89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,68 +6599,69 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-53000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-43900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-44200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-38300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-46500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-38700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-35800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-24900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-30500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-34300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-31200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-52500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-21100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-21800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-16300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4200</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>5</v>
       </c>
@@ -6456,8 +6677,11 @@
       <c r="AA91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,68 +6837,71 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-89100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-575000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-537600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-146800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-624900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-15900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-777200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-301000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-692200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>117300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1025700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-166000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-190100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-629500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>84300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-199700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-548900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-357800</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>5</v>
       </c>
@@ -6687,8 +6917,11 @@
       <c r="AA94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6745,8 +6979,8 @@
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,68 +7267,71 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-245600</v>
+      </c>
+      <c r="E100" s="3">
         <v>144100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>465600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>146000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>112000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>506300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>148800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>609500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-129000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>669800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>199500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-28900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>55800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1766300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>244000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-176100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1488600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>447500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>817800</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>5</v>
       </c>
@@ -7101,59 +7347,62 @@
       <c r="AA100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E101" s="3">
         <v>3700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-11100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-11100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2700</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>5</v>
       </c>
@@ -7166,8 +7415,8 @@
       <c r="W101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
+      <c r="X101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y101" s="3">
         <v>0</v>
@@ -7178,68 +7427,71 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E102" s="3">
         <v>352500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>89200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-324300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>171700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-40500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>228500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-121500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-483300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-48700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>362700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1124800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-139200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1139000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-16800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-114400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1170200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-149100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>457700</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>5</v>
       </c>
@@ -7253,6 +7505,9 @@
         <v>5</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AFRM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFRM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
   <si>
     <t>AFRM</t>
   </si>
@@ -656,258 +656,264 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1123000</v>
+      </c>
+      <c r="E8" s="3">
         <v>933300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>876400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>783100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>866400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>698500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>659200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>576200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>591100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>496500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>445800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>381000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>340000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>298000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>308900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>302300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>303300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>238400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>219200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>214300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>189500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>157500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>141800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>128400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>125200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>82200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>69600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>73100</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>580500</v>
+      </c>
+      <c r="E9" s="3">
         <v>478100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>451300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>430600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>447000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>413400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>349800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>345200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>349300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>284200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>263700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>214100</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
@@ -953,47 +959,50 @@
       <c r="AD9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>542500</v>
+      </c>
+      <c r="E10" s="3">
         <v>455200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>425100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>352600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>419400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>285100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>309400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>230900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>241800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>212400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>182100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>166900</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1039,8 +1048,11 @@
       <c r="AD10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1071,47 +1083,48 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>184900</v>
+      </c>
+      <c r="E12" s="3">
         <v>168100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>154600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>152600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>148200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>134300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>124200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>124800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>119800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>133000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>152300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>161800</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>5</v>
       </c>
@@ -1157,8 +1170,11 @@
       <c r="AD12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1243,133 +1259,139 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-100</v>
       </c>
-      <c r="G14" s="3">
-        <v>-82400</v>
-      </c>
       <c r="H14" s="3">
+        <v>100</v>
+      </c>
+      <c r="I14" s="3">
         <v>-16900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-13200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>5200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>15200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-87600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>34900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-21200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-28000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-15000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-5600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>7600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>20700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>24300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>57200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>55200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>49400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>43700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>33700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>37900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>14200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>22000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>80400</v>
+      </c>
+      <c r="E15" s="3">
         <v>73400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>72000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>70400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>69100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>61000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>79500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>52900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>48100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>61700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>64600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>68600</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1415,8 +1437,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1005400</v>
+      </c>
+      <c r="E17" s="3">
         <v>869700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>819200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>791500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>870600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>831400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>731000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>731700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>762200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>703600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>687400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>656100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>699500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>585500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>586100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>528800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>499500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>404500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>333500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>423700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>216300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>190800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>102400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>209900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>157900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>115200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>110300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>117600</v>
+      </c>
+      <c r="E18" s="3">
         <v>63700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>57300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-132900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-71900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-155600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-171100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-207000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-241500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-275100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-359500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-287500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-277200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-226500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-196200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-166100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-114300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-209400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-26800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-33300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>39400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-81500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-32700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-33000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-40700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-20300</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,180 +1680,187 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-20600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-17800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-16300</v>
       </c>
-      <c r="G20" s="3">
-        <v>-5800</v>
-      </c>
       <c r="H20" s="3">
+        <v>-88200</v>
+      </c>
+      <c r="I20" s="3">
         <v>-18400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-15300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-28600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-19500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-39600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>52500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-104500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>35500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>36000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>72700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>172100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>36800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-140400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-11600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-77800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>29500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>4300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>216300</v>
+      </c>
+      <c r="E21" s="3">
         <v>157600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>147000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>78300</v>
       </c>
-      <c r="G21" s="3">
-        <v>70600</v>
-      </c>
       <c r="H21" s="3">
+        <v>153100</v>
+      </c>
+      <c r="I21" s="3">
         <v>-53500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>23000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-74100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-103500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-105700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-229400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-102000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-301000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-230600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-187400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-41300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-147500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-295900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-118000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-282100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-23200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-100</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-28600</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1835,16 +1874,16 @@
         <v>2700</v>
       </c>
       <c r="G22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="H22" s="3">
         <v>1000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>800</v>
       </c>
       <c r="I22" s="3">
         <v>800</v>
       </c>
       <c r="J22" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="K22" s="3">
         <v>900</v>
@@ -1853,14 +1892,14 @@
         <v>900</v>
       </c>
       <c r="M22" s="3">
+        <v>900</v>
+      </c>
+      <c r="N22" s="3">
         <v>800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1000</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
@@ -1906,156 +1945,162 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>133200</v>
+      </c>
+      <c r="E23" s="3">
         <v>83000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>71600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>82900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-98300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-44100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-133000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-167600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-170700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-207300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-206500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-324000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-251400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-204500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-54400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-159500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-306400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-125900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-287100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-26500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>34900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-85500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-30900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-30700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-36400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-19700</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>2300</v>
+        <v>3700</v>
       </c>
       <c r="E24" s="3">
         <v>2300</v>
       </c>
       <c r="F24" s="3">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="G24" s="3">
         <v>2500</v>
       </c>
       <c r="H24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I24" s="3">
         <v>1900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-18100</v>
-      </c>
-      <c r="R24" s="3">
-        <v>300</v>
       </c>
       <c r="S24" s="3">
         <v>300</v>
       </c>
       <c r="T24" s="3">
+        <v>300</v>
+      </c>
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-2400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-100</v>
-      </c>
-      <c r="W24" s="3">
-        <v>100</v>
       </c>
       <c r="X24" s="3">
         <v>100</v>
@@ -2073,13 +2118,16 @@
         <v>100</v>
       </c>
       <c r="AC24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>129600</v>
+      </c>
+      <c r="E26" s="3">
         <v>80700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>69200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>80400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-100200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-45100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-133900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-166900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-171800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-206000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-205700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-322400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-251300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-186400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-54700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-159700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-306600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-123400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-287100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-26600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>34800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-85600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-31000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-30800</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD26" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>129600</v>
+      </c>
+      <c r="E27" s="3">
         <v>80700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>69200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>80400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-100200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-45100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-133900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-166900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-171800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-206000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-205700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-322400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-251300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-186400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-54700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-159700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-306600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-123400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-287100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-26600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>34800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-85600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-44200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-30800</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD27" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2508,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,180 +2746,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E32" s="3">
         <v>20600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>17800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>16300</v>
       </c>
-      <c r="G32" s="3">
-        <v>5800</v>
-      </c>
       <c r="H32" s="3">
+        <v>88200</v>
+      </c>
+      <c r="I32" s="3">
         <v>18400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>15300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>28600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>19500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>39600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-52500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>104500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-35500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-36000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-72700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-172100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-36800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>140400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>11600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>77800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-29500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>4500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>4000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>129600</v>
+      </c>
+      <c r="E33" s="3">
         <v>80700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>69200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>80400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-100200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-45100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-133900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-166900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-171800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-206000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-205700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-322400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-251300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-186400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-54700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-159700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-306600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-123400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-287100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-26600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>34800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-85600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-44200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-30800</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD33" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>129600</v>
+      </c>
+      <c r="E35" s="3">
         <v>80700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>69200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>80400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-100200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-45100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-133900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-166900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-171800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-206000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-205700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-322400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-251300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-186400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-54700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-159700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-306600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-123400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-287100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-26600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>34800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-85600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-44200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-30800</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD35" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,77 +3264,78 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1527900</v>
+      </c>
+      <c r="E41" s="3">
         <v>1428800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1354500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1351100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1200400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1046200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1013100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1272800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1036700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1079300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>892000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>972500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1440300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1530100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1255200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2261900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2567400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1439500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1466600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1623700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>520700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>684400</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>5</v>
       </c>
@@ -3265,47 +3351,50 @@
       <c r="AD41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>36600</v>
+      </c>
+      <c r="E42" s="3">
         <v>48900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>39000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>8700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>39400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>848600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>69700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>582700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>685400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>86500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>97200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>145500</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -3351,77 +3440,80 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>268200</v>
+      </c>
+      <c r="E43" s="3">
         <v>283700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>429900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>231900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>216800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>325000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>371300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>312700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>307300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>236200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>216300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>135800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>201600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>147800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>142100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>124600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>134600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>101000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>91600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>66100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>67000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>49000</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>5</v>
       </c>
@@ -3437,8 +3529,11 @@
       <c r="AD43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3475,8 +3570,8 @@
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3523,8 +3618,11 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3561,33 +3659,33 @@
       <c r="N45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P45" s="3">
         <v>14300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>15100</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>35200</v>
       </c>
       <c r="R45" s="3">
         <v>35200</v>
       </c>
       <c r="S45" s="3">
+        <v>35200</v>
+      </c>
+      <c r="T45" s="3">
         <v>37300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>23300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>111300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>90900</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>5</v>
       </c>
@@ -3603,53 +3701,56 @@
       <c r="AB45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC45" s="3">
-        <v>0</v>
+      <c r="AC45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2485900</v>
+      </c>
+      <c r="E46" s="3">
         <v>2508200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2297600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2053900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2049900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2613400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1786600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2567000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2543900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1866400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1623500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1692800</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -3695,77 +3796,80 @@
       <c r="AD46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9022700</v>
+      </c>
+      <c r="E47" s="3">
         <v>7613300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>7503900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7073000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7131300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6249700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6513100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5465600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5290900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5304400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5369600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4605300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4453200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3826600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4003900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3008600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2790300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2585000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1958400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2099100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1757700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1290300</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3781,77 +3885,80 @@
       <c r="AD47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>665800</v>
+      </c>
+      <c r="E48" s="3">
         <v>630700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>591800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>564800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>523800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>492700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>449500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>425600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>394900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>366000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>320300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>311200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>292600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>256200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>222200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>194000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>169400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>143500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>120300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>113100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>49400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>49600</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3867,71 +3974,74 @@
       <c r="AD48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>546100</v>
+      </c>
+      <c r="E49" s="3">
         <v>542600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>547100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>534800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>533900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>550200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>546900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>551100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>558600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>556200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>577000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>585400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>591400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>596000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>618500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>608300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>607600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>612100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>584400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>279200</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3947,14 +4057,17 @@
       <c r="AB49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC49" s="3">
-        <v>0</v>
+      <c r="AC49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,77 +4241,80 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>226900</v>
+      </c>
+      <c r="E52" s="3">
         <v>171800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>200600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>194500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>224300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>212900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>202200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>171000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>254000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>314200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>242000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>313100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>459100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>422300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>335800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>440500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>298700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>256000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>260200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>216800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>137500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>112200</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>5</v>
       </c>
@@ -4211,8 +4330,11 @@
       <c r="AD52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,77 +4419,80 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12956900</v>
+      </c>
+      <c r="E54" s="3">
         <v>11478600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>11154900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10436200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10481100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10139200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9519600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>9201400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9065000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8407100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8155600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7507800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7804800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7165100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6973800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7031700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6952400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5402100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4867000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4766400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2708100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2250500</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>5</v>
       </c>
@@ -4383,8 +4508,11 @@
       <c r="AD54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,77 +4576,78 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>57200</v>
+      </c>
+      <c r="E57" s="3">
         <v>58000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>82800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>41100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>50600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>57600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>41000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>35200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>59800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>27300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>28600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>30000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>29000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>34500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>33100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>49000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>45600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>425900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>57800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>29000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>26200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>24500</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>5</v>
       </c>
@@ -4533,38 +4663,41 @@
       <c r="AD57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E58" s="3">
         <v>12300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>16600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12600</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>4100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10200</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4619,77 +4752,80 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3">
         <v>2800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>21200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>23300</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N59" s="3">
         <v>53300</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P59" s="3">
         <v>249700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>220900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>211100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>151400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>213200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>180000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>200800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>177700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>80800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>49200</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4705,47 +4841,50 @@
       <c r="AD59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>179500</v>
+      </c>
+      <c r="E60" s="3">
         <v>171700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>199500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>152400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>166800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>156400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>142600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>144100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>168900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>89100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>146100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>83800</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -4791,77 +4930,80 @@
       <c r="AD60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9173700</v>
+      </c>
+      <c r="E61" s="3">
         <v>7946000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7836700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7354100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7487600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7107300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6614300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6408700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6233200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5682200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5451000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4816500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4905700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4221200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4006800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4054400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3927900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2106500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1857300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2001500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1623400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1197800</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -4877,47 +5019,50 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>56800</v>
+      </c>
+      <c r="E62" s="3">
         <v>62100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>49700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>54800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>41200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>39800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>30700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>25100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>28000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>69100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>24400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>96400</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
@@ -4963,8 +5108,11 @@
       <c r="AD62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,77 +5375,80 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9410000</v>
+      </c>
+      <c r="E66" s="3">
         <v>8179700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8085900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7561300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7695500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7303600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6787600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6578000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6430100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5840300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5621400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4996700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5294600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4601600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4355500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4455700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4484100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3024700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2285800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2362400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1730400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1271500</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>5</v>
       </c>
@@ -5307,8 +5464,11 @@
       <c r="AD66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5574,14 +5741,14 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
         <v>1327300</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>1327200</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
       <c r="Z70" s="3">
         <v>0</v>
       </c>
@@ -5597,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,77 +5853,80 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2846500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2976100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3056800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-3126100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3128900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3209200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3109000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-3063900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2929900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2763000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2591200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2385300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2179600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1857200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1605900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1419500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1364800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1205100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-888400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-734900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-494000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-462400</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>5</v>
       </c>
@@ -5769,8 +5942,11 @@
       <c r="AD72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,77 +6209,80 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3546900</v>
+      </c>
+      <c r="E76" s="3">
         <v>3298900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3069000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2874900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2785500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2835600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2732000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2623500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2634900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2566800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2534200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2511100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2510100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2563400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2618300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2576100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2468300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2377400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2581200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2404000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-349600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-348100</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>5</v>
       </c>
@@ -6113,8 +6298,11 @@
       <c r="AD76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>129600</v>
+      </c>
+      <c r="E81" s="3">
         <v>80700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>69200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>80400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-100200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-45100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-133900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-166900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-171800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-206000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-205700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-322400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-251300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-186400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-54700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-159700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-306600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-123400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-287100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-26600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>34800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-85600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-44200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-30800</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD81" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,77 +6605,78 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>54300</v>
+      </c>
+      <c r="E83" s="3">
         <v>46100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>63600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>35100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>23600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>25900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>29200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>23900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>20900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>10000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>23000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>20900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>17100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>13100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>10500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>7900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>5000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3700</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>5</v>
       </c>
@@ -6494,8 +6692,11 @@
       <c r="AD83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,77 +7137,80 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>173700</v>
+      </c>
+      <c r="E89" s="3">
         <v>374600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>74600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>210400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>312000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>196900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>68800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>208200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>74300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>98900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>43800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-54300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-28500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>51200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-59100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-28000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-440300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>365200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-19900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-123300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-47700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>5</v>
       </c>
@@ -7010,8 +7226,11 @@
       <c r="AD89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,77 +7261,78 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-55700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-54400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-51100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-53000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-43900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-44200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-38300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-46500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-38700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-35800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-24900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-30500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-34300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-31200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-52500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-21100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-21800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-16300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>5</v>
       </c>
@@ -7128,8 +7348,11 @@
       <c r="AD91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,77 +7526,80 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1365000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-139600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-454500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>35500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-89100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-575000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-537600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-146800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-624900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-15900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-777200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-301000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-692200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>117300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1025700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-166000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-190100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-629500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>84300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-199700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-548900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-357800</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>5</v>
       </c>
@@ -7386,8 +7615,11 @@
       <c r="AD94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7456,8 +7689,8 @@
       <c r="N96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7504,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,77 +8004,80 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1186600</v>
+      </c>
+      <c r="E100" s="3">
         <v>110100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>387300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-245600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>144100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>465600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>146000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>112000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>506300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>148800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>609500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-129000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>669800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>199500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-28900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>55800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1766300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>244000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-176100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1488600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>447500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>817800</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>5</v>
       </c>
@@ -7848,68 +8093,71 @@
       <c r="AD100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="E101" s="3">
         <v>1700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-11100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-11100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>3000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>3600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2700</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W101" s="3" t="s">
         <v>5</v>
       </c>
@@ -7922,8 +8170,8 @@
       <c r="Z101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
+      <c r="AA101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB101" s="3">
         <v>0</v>
@@ -7934,77 +8182,80 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E102" s="3">
         <v>341200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>20500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>352500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>89200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-324300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>171700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-40500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>228500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-121500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-483300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-48700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>362700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1124800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-139200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1139000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-16800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-114400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1170200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-149100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>457700</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>5</v>
       </c>
@@ -8018,6 +8269,9 @@
         <v>5</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AFRM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFRM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="92">
   <si>
     <t>AFRM</t>
   </si>
@@ -656,267 +656,274 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1038800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1123000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>933300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>876400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>783100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>866400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>698500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>659200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>576200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>591100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>496500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>445800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>381000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>340000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>298000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>308900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>302300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>303300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>238400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>219200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>214300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>189500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>157500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>141800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>128400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>125200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>82200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>69600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>73100</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>540600</v>
+      </c>
+      <c r="E9" s="3">
         <v>580500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>478100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>451300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>430600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>447000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>413400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>349800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>345200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>349300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>284200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>263700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>214100</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
@@ -962,50 +969,53 @@
       <c r="AE9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>498200</v>
+      </c>
+      <c r="E10" s="3">
         <v>542500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>455200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>425100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>352600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>419400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>285100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>309400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>230900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>241800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>212400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>182100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>166900</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1051,8 +1061,11 @@
       <c r="AE10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,50 +1097,51 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>191600</v>
+      </c>
+      <c r="E12" s="3">
         <v>184900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>168100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>154600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>152600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>148200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>134300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>124200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>124800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>119800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>133000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>152300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>161800</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>5</v>
       </c>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,139 +1279,145 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>-1500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-16900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-13200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>5200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>15200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-87600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>34900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-21200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-28000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-15000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-5600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>7600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>20700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>24300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>57200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>55200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>49400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>43700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>33700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>37900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>14200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>22000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>78100</v>
+      </c>
+      <c r="E15" s="3">
         <v>80400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>73400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>72000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>70400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>69100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>61000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>79500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>52900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>48100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>61700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>64600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>68600</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>950300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1005400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>869700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>819200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>791500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>870600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>831400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>731000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>731700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>762200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>703600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>687400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>656100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>699500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>585500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>586100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>528800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>499500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>404500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>333500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>423700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>216300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>190800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>102400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>209900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>157900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>115200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>110300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>88400</v>
+      </c>
+      <c r="E18" s="3">
         <v>117600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>63700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>57300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-132900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-71900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-155600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-171100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-207000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-241500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-275100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-359500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-287500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-277200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-226500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-196200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-166100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-114300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-209400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-26800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-33300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>39400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-81500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-32700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-33000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-40700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-20300</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,186 +1714,193 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-18300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-20600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-17800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-16300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-88200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-18400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-15300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-28600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-19500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-39600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>52500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-104500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>35500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>36000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>72700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>172100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>36800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-140400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-11600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-77800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>29500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>4300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>188100</v>
+      </c>
+      <c r="E21" s="3">
         <v>216300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>157600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>147000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>78300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>153100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-53500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>23000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-74100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-103500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-105700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-229400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-102000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-301000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-230600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-187400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-41300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-147500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-295900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-118000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-282100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-23200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-100</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-28600</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1877,16 +1917,16 @@
         <v>2700</v>
       </c>
       <c r="H22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I22" s="3">
         <v>1000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>800</v>
       </c>
       <c r="J22" s="3">
         <v>800</v>
       </c>
       <c r="K22" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="L22" s="3">
         <v>900</v>
@@ -1895,14 +1935,14 @@
         <v>900</v>
       </c>
       <c r="N22" s="3">
+        <v>900</v>
+      </c>
+      <c r="O22" s="3">
         <v>800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1000</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
@@ -1948,162 +1988,168 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>107400</v>
+      </c>
+      <c r="E23" s="3">
         <v>133200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>83000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>71600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>82900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-98300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-44100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-133000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-167600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-170700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-207300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-206500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-324000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-251400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-204500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-54400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-159500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-306400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-125900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-287100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-26500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>34900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-85500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-30900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-30700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-36400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-19700</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E24" s="3">
         <v>3700</v>
-      </c>
-      <c r="E24" s="3">
-        <v>2300</v>
       </c>
       <c r="F24" s="3">
         <v>2300</v>
       </c>
       <c r="G24" s="3">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="H24" s="3">
         <v>2500</v>
       </c>
       <c r="I24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J24" s="3">
         <v>1900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-18100</v>
-      </c>
-      <c r="S24" s="3">
-        <v>300</v>
       </c>
       <c r="T24" s="3">
         <v>300</v>
       </c>
       <c r="U24" s="3">
+        <v>300</v>
+      </c>
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-2400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-100</v>
-      </c>
-      <c r="X24" s="3">
-        <v>100</v>
       </c>
       <c r="Y24" s="3">
         <v>100</v>
@@ -2121,13 +2167,16 @@
         <v>100</v>
       </c>
       <c r="AD24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>102900</v>
+      </c>
+      <c r="E26" s="3">
         <v>129600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>80700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>69200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>80400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-100200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-45100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-133900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-166900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-171800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-206000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-205700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-322400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-251300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-186400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-54700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-159700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-306600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-123400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-287100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-26600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>34800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-85600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-31000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-30800</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE26" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>102900</v>
+      </c>
+      <c r="E27" s="3">
         <v>129600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>80700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>69200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>80400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-100200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-45100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-133900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-166900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-171800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-206000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-205700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-322400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-251300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-186400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-54700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-159700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-306600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-123400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-287100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-26600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>34800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-85600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-44200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-30800</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE27" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,186 +2816,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E32" s="3">
         <v>18300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>20600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>17800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>16300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>88200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>18400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>15300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>28600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>19500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>39600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-52500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>104500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-35500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-36000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-72700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-172100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-36800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>140400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>11600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>77800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-29500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>4500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>4000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>102900</v>
+      </c>
+      <c r="E33" s="3">
         <v>129600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>80700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>69200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>80400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-100200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-45100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-133900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-166900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-171800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-206000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-205700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-322400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-251300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-186400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-54700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-159700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-306600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-123400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-287100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-26600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>34800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-85600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-44200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-30800</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE33" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>102900</v>
+      </c>
+      <c r="E35" s="3">
         <v>129600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>80700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>69200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>80400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-100200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-45100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-133900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-166900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-171800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-206000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-205700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-322400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-251300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-186400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-54700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-159700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-306600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-123400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-287100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-26600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>34800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-85600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-44200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-30800</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE35" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,80 +3351,81 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1723400</v>
+      </c>
+      <c r="E41" s="3">
         <v>1527900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1428800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1354500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1351100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1200400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1046200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1013100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1272800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1036700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1079300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>892000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>972500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1440300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1530100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1255200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2261900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2567400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1439500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1466600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1623700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>520700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>684400</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>5</v>
       </c>
@@ -3354,50 +3441,53 @@
       <c r="AE41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E42" s="3">
         <v>36600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>48900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>39000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>8700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>39400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>848600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>69700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>582700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>685400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>86500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>97200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>145500</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -3443,80 +3533,83 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>230700</v>
+      </c>
+      <c r="E43" s="3">
         <v>268200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>283700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>429900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>231900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>216800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>325000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>371300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>312700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>307300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>236200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>216300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>135800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>201600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>147800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>142100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>124600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>134600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>101000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>91600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>66100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>67000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>49000</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>5</v>
       </c>
@@ -3532,8 +3625,11 @@
       <c r="AE43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3573,8 +3669,8 @@
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3621,8 +3717,11 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3662,33 +3761,33 @@
       <c r="O45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q45" s="3">
         <v>14300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>15100</v>
-      </c>
-      <c r="R45" s="3">
-        <v>35200</v>
       </c>
       <c r="S45" s="3">
         <v>35200</v>
       </c>
       <c r="T45" s="3">
+        <v>35200</v>
+      </c>
+      <c r="U45" s="3">
         <v>37300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>23300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>111300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>90900</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>5</v>
       </c>
@@ -3704,56 +3803,59 @@
       <c r="AC45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD45" s="3">
-        <v>0</v>
+      <c r="AD45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2829000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2485900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2508200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2297600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2053900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2049900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2613400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1786600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2567000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2543900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1866400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1623500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1692800</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -3799,80 +3901,83 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8815500</v>
+      </c>
+      <c r="E47" s="3">
         <v>9022700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>7613300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7503900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7073000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7131300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6249700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6513100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5465600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5290900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5304400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5369600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4605300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4453200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3826600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4003900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3008600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2790300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2585000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1958400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2099100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1757700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1290300</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3888,80 +3993,83 @@
       <c r="AE47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>691800</v>
+      </c>
+      <c r="E48" s="3">
         <v>665800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>630700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>591800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>564800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>523800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>492700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>449500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>425600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>394900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>366000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>320300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>311200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>292600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>256200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>222200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>194000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>169400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>143500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>120300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>113100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>49400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>49600</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3977,74 +4085,77 @@
       <c r="AE48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>556700</v>
+      </c>
+      <c r="E49" s="3">
         <v>546100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>542600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>547100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>534800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>533900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>550200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>546900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>551100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>558600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>556200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>577000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>585400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>591400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>596000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>618500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>608300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>607600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>612100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>584400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>279200</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>5</v>
       </c>
@@ -4060,14 +4171,17 @@
       <c r="AC49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD49" s="3">
-        <v>0</v>
+      <c r="AD49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,80 +4361,83 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>241100</v>
+      </c>
+      <c r="E52" s="3">
         <v>226900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>171800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>200600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>194500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>224300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>212900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>202200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>171000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>254000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>314200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>242000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>313100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>459100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>422300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>335800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>440500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>298700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>256000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>260200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>216800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>137500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>112200</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>5</v>
       </c>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,80 +4545,83 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13141600</v>
+      </c>
+      <c r="E54" s="3">
         <v>12956900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>11478600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>11154900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10436200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10481100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10139200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>9519600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9201400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9065000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8407100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8155600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7507800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7804800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7165100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6973800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7031700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6952400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5402100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4867000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4766400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2708100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2250500</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>5</v>
       </c>
@@ -4511,8 +4637,11 @@
       <c r="AE54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,80 +4707,81 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E57" s="3">
         <v>57200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>58000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>82800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>41100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>50600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>57600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>41000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>35200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>59800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>27300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>28600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>30000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>29000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>34500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>33100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>49000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>45600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>425900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>57800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>29000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>26200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>24500</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>5</v>
       </c>
@@ -4666,41 +4797,44 @@
       <c r="AE57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E58" s="3">
         <v>8100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>16600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>12600</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>4100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>10200</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4755,8 +4889,11 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4766,69 +4903,69 @@
       <c r="E59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3">
         <v>2800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>17600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>21200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>23300</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O59" s="3">
         <v>53300</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q59" s="3">
         <v>249700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>220900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>211100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>151400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>213200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>180000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>200800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>177700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>80800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>49200</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4844,50 +4981,53 @@
       <c r="AE59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>208900</v>
+      </c>
+      <c r="E60" s="3">
         <v>179500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>171700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>199500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>152400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>166800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>156400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>142600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>144100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>168900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>89100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>146100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>83800</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -4933,80 +5073,83 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9087000</v>
+      </c>
+      <c r="E61" s="3">
         <v>9173700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7946000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7836700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7354100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7487600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7107300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6614300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6408700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6233200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5682200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5451000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4816500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4905700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4221200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4006800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4054400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3927900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2106500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1857300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2001500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1623400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1197800</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5022,50 +5165,53 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>62300</v>
+      </c>
+      <c r="E62" s="3">
         <v>56800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>62100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>49700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>54800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>41200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>39800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>30700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>25100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>28000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>69100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>24400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>96400</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,80 +5533,83 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9358200</v>
+      </c>
+      <c r="E66" s="3">
         <v>9410000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8179700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8085900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7561300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7695500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7303600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6787600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6578000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6430100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5840300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5621400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4996700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5294600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4601600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4355500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4455700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4484100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3024700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2285800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2362400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1730400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1271500</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>5</v>
       </c>
@@ -5467,8 +5625,11 @@
       <c r="AE66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5744,14 +5912,14 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
         <v>1327300</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>1327200</v>
       </c>
-      <c r="Z70" s="3">
-        <v>0</v>
-      </c>
       <c r="AA70" s="3">
         <v>0</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,80 +6027,83 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2743600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2846500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2976100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-3056800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3126100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3128900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3209200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-3109000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-3063900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2929900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2763000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2591200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2385300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2179600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1857200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1605900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1419500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1364800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1205100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-888400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-734900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-494000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-462400</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>5</v>
       </c>
@@ -5945,8 +6119,11 @@
       <c r="AE72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,80 +6395,83 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3783400</v>
+      </c>
+      <c r="E76" s="3">
         <v>3546900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3298900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3069000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2874900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2785500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2835600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2732000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2623500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2634900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2566800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2534200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2511100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2510100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2563400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2618300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2576100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2468300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2377400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2581200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2404000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-349600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-348100</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>5</v>
       </c>
@@ -6301,8 +6487,11 @@
       <c r="AE76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>102900</v>
+      </c>
+      <c r="E81" s="3">
         <v>129600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>80700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>69200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>80400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-100200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-45100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-133900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-166900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-171800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-206000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-205700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-322400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-251300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-186400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-54700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-159700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-306600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-123400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-287100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-26600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>34800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-85600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-44200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-30800</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE81" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,80 +6804,81 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>59400</v>
+      </c>
+      <c r="E83" s="3">
         <v>54300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>46100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>63600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>35100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>23600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>25900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>29200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>23900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>20900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>10000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>23000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>20900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>17100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>13100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>10500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>7900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>5000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3700</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>5</v>
       </c>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,80 +7354,83 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>386500</v>
+      </c>
+      <c r="E89" s="3">
         <v>173700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>374600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>74600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>210400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>312000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>196900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>68800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>208200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>74300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>98900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>43800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-54300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-28500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>51200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-59100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-28000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-440300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>365200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-19900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-123300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-47700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>5</v>
       </c>
@@ -7229,8 +7446,11 @@
       <c r="AE89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,80 +7482,81 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-61400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-55700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-54400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-51100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-53000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-43900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-44200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-38300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-46500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-38700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-35800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-24900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-30500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-34300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-31200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-52500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-21100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-21800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-16300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>5</v>
       </c>
@@ -7351,8 +7572,11 @@
       <c r="AE91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,80 +7756,83 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>149400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1365000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-139600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-454500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>35500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-89100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-575000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-537600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-146800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-624900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-777200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-301000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-692200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>117300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1025700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-166000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-190100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-629500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>84300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-199700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-548900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-357800</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>5</v>
       </c>
@@ -7618,8 +7848,11 @@
       <c r="AE94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7692,8 +7926,8 @@
       <c r="O96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,80 +8250,83 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-152600</v>
+      </c>
+      <c r="E100" s="3">
         <v>1186600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>110100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>387300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-245600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>144100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>465600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>146000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>112000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>506300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>148800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>609500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-129000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>669800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>199500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-28900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>55800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1766300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>244000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-176100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1488600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>447500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>817800</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>5</v>
       </c>
@@ -8096,71 +8342,74 @@
       <c r="AE100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-14500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>3700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-11100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-5300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-11100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>3000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>3600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2700</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X101" s="3" t="s">
         <v>5</v>
       </c>
@@ -8173,8 +8422,8 @@
       <c r="AA101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
+      <c r="AB101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC101" s="3">
         <v>0</v>
@@ -8185,80 +8434,83 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>379700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>341200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>20500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>352500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>89200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-324300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>171700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-40500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>228500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-121500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-483300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-48700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>362700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1124800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-139200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1139000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-16800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-114400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1170200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-149100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>457700</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>5</v>
       </c>
@@ -8272,6 +8524,9 @@
         <v>5</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
